--- a/meds/list.xlsx
+++ b/meds/list.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C448D75-A072-42F3-BFB0-7FACDFD4C022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56720AE0-55AE-4751-A825-9B38A563E2E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="396">
   <si>
     <t>S.No.</t>
   </si>
@@ -1250,13 +1250,16 @@
   </si>
   <si>
     <t>Total MRP</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1283,6 +1286,14 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1298,7 +1309,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1334,11 +1345,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1348,13 +1372,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1635,7 +1664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M403"/>
+  <dimension ref="A1:M405"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
@@ -1648,37 +1677,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5" t="s">
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="7" t="s">
+      <c r="K1" s="9"/>
+      <c r="L1" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="2" t="s">
         <v>389</v>
       </c>
@@ -1697,11 +1726,11 @@
       <c r="H2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -1723,8 +1752,16 @@
       <c r="I3" s="3">
         <v>86.9</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>63</v>
+      </c>
+      <c r="L3" s="3">
+        <f>G3*I3</f>
+        <v>1738</v>
+      </c>
+      <c r="M3" s="3">
+        <f>G3*J3</f>
+        <v>1260</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -1748,6 +1785,14 @@
       <c r="J4" s="3">
         <v>115</v>
       </c>
+      <c r="L4" s="3">
+        <f t="shared" ref="L4:L20" si="0">G4*I4</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <f t="shared" ref="M4:M20" si="1">G4*J4</f>
+        <v>805</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -1772,6 +1817,14 @@
       <c r="J5" s="3">
         <v>170</v>
       </c>
+      <c r="L5" s="3">
+        <f t="shared" si="0"/>
+        <v>1040</v>
+      </c>
+      <c r="M5" s="3">
+        <f t="shared" si="1"/>
+        <v>1360</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
@@ -1794,6 +1847,14 @@
       <c r="J6" s="3">
         <v>150</v>
       </c>
+      <c r="L6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -1814,6 +1875,14 @@
       <c r="J7" s="3">
         <v>80</v>
       </c>
+      <c r="L7" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <f t="shared" si="1"/>
+        <v>1360</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
@@ -1838,6 +1907,14 @@
       <c r="J8" s="3">
         <v>65</v>
       </c>
+      <c r="L8" s="3">
+        <f t="shared" si="0"/>
+        <v>840.75</v>
+      </c>
+      <c r="M8" s="3">
+        <f t="shared" si="1"/>
+        <v>975</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -1860,6 +1937,14 @@
       <c r="J9" s="3">
         <v>150</v>
       </c>
+      <c r="L9" s="3">
+        <f t="shared" si="0"/>
+        <v>1032</v>
+      </c>
+      <c r="M9" s="3">
+        <f t="shared" si="1"/>
+        <v>1200</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
@@ -1884,6 +1969,14 @@
       <c r="J10" s="3">
         <v>20</v>
       </c>
+      <c r="L10" s="3">
+        <f t="shared" si="0"/>
+        <v>534.75</v>
+      </c>
+      <c r="M10" s="3">
+        <f t="shared" si="1"/>
+        <v>620</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -1906,6 +1999,14 @@
       <c r="J11" s="3">
         <v>10</v>
       </c>
+      <c r="L11" s="3">
+        <f t="shared" si="0"/>
+        <v>94.82</v>
+      </c>
+      <c r="M11" s="3">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
@@ -1930,6 +2031,14 @@
       <c r="J12" s="3">
         <v>10</v>
       </c>
+      <c r="L12" s="3">
+        <f t="shared" si="0"/>
+        <v>163.97000000000003</v>
+      </c>
+      <c r="M12" s="3">
+        <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -1952,6 +2061,14 @@
       <c r="J13" s="3">
         <v>30</v>
       </c>
+      <c r="L13" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -1974,6 +2091,14 @@
       <c r="J14" s="3">
         <v>5.64</v>
       </c>
+      <c r="L14" s="3">
+        <f t="shared" si="0"/>
+        <v>46.62</v>
+      </c>
+      <c r="M14" s="3">
+        <f t="shared" si="1"/>
+        <v>33.839999999999996</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -1998,6 +2123,14 @@
       <c r="J15" s="3">
         <v>42</v>
       </c>
+      <c r="L15" s="3">
+        <f t="shared" si="0"/>
+        <v>362.2</v>
+      </c>
+      <c r="M15" s="3">
+        <f t="shared" si="1"/>
+        <v>420</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
@@ -2020,8 +2153,16 @@
       <c r="J16" s="3">
         <v>34</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L16" s="3">
+        <f t="shared" si="0"/>
+        <v>609.57000000000005</v>
+      </c>
+      <c r="M16" s="3">
+        <f t="shared" si="1"/>
+        <v>442</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -2040,8 +2181,16 @@
       <c r="J17" s="3">
         <v>150</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L17" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -2064,8 +2213,16 @@
       <c r="J18" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L18" s="3">
+        <f t="shared" si="0"/>
+        <v>1939.5</v>
+      </c>
+      <c r="M18" s="3">
+        <f t="shared" si="1"/>
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -2088,8 +2245,16 @@
       <c r="J19" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L19" s="3">
+        <f t="shared" si="0"/>
+        <v>181.23000000000002</v>
+      </c>
+      <c r="M19" s="3">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -2112,8 +2277,16 @@
       <c r="J20" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L20" s="3">
+        <f t="shared" si="0"/>
+        <v>414.24</v>
+      </c>
+      <c r="M20" s="3">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -2134,8 +2307,16 @@
       <c r="J21" s="3">
         <v>110</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L21" s="3">
+        <f>E21*I21</f>
+        <v>320</v>
+      </c>
+      <c r="M21" s="3">
+        <f>E21*J21</f>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -2156,8 +2337,16 @@
       <c r="J22" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L22" s="3">
+        <f t="shared" ref="L22:L30" si="2">E22*I22</f>
+        <v>240</v>
+      </c>
+      <c r="M22" s="3">
+        <f t="shared" ref="M22:M30" si="3">E22*J22</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -2178,8 +2367,16 @@
       <c r="J23" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L23" s="3">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="M23" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -2198,8 +2395,16 @@
       <c r="J24" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <f t="shared" si="3"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -2220,8 +2425,16 @@
       <c r="J25" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L25" s="3">
+        <f t="shared" si="2"/>
+        <v>1600</v>
+      </c>
+      <c r="M25" s="3">
+        <f t="shared" si="3"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -2242,8 +2455,16 @@
       <c r="J26" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L26" s="3">
+        <f t="shared" si="2"/>
+        <v>1075</v>
+      </c>
+      <c r="M26" s="3">
+        <f t="shared" si="3"/>
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -2265,8 +2486,16 @@
       <c r="J27" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L27" s="3">
+        <f t="shared" si="2"/>
+        <v>1620</v>
+      </c>
+      <c r="M27" s="3">
+        <f t="shared" si="3"/>
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -2287,8 +2516,16 @@
       <c r="J28" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L28" s="3">
+        <f t="shared" si="2"/>
+        <v>675</v>
+      </c>
+      <c r="M28" s="3">
+        <f t="shared" si="3"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -2309,8 +2546,16 @@
       <c r="J29" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L29" s="3">
+        <f t="shared" si="2"/>
+        <v>875</v>
+      </c>
+      <c r="M29" s="3">
+        <f t="shared" si="3"/>
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -2331,8 +2576,16 @@
       <c r="J30" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L30" s="3">
+        <f t="shared" si="2"/>
+        <v>525</v>
+      </c>
+      <c r="M30" s="3">
+        <f t="shared" si="3"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -2355,8 +2608,16 @@
       <c r="J31" s="3">
         <v>142.5</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L31" s="3">
+        <f>G31*I31</f>
+        <v>589.62</v>
+      </c>
+      <c r="M31" s="3">
+        <f>G31*J31</f>
+        <v>427.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -2379,8 +2640,16 @@
       <c r="J32" s="3">
         <v>210</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L32" s="3">
+        <f t="shared" ref="L32:L53" si="4">G32*I32</f>
+        <v>2715.75</v>
+      </c>
+      <c r="M32" s="3">
+        <f t="shared" ref="M32:M53" si="5">G32*J32</f>
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -2401,8 +2670,16 @@
       <c r="J33" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L33" s="3">
+        <f t="shared" si="4"/>
+        <v>2898</v>
+      </c>
+      <c r="M33" s="3">
+        <f t="shared" si="5"/>
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -2425,8 +2702,16 @@
       <c r="J34" s="3">
         <v>160</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L34" s="3">
+        <f t="shared" si="4"/>
+        <v>7726.8799999999992</v>
+      </c>
+      <c r="M34" s="3">
+        <f t="shared" si="5"/>
+        <v>8960</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -2447,8 +2732,16 @@
       <c r="J35" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L35" s="3">
+        <f t="shared" si="4"/>
+        <v>621</v>
+      </c>
+      <c r="M35" s="3">
+        <f t="shared" si="5"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>34</v>
       </c>
@@ -2465,8 +2758,16 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L36" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -2489,8 +2790,16 @@
       <c r="J37" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L37" s="3">
+        <f t="shared" si="4"/>
+        <v>413.76</v>
+      </c>
+      <c r="M37" s="3">
+        <f t="shared" si="5"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>36</v>
       </c>
@@ -2509,8 +2818,16 @@
       <c r="J38" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L38" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M38" s="3">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -2527,8 +2844,16 @@
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L39" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -2547,8 +2872,16 @@
       <c r="J40" s="3">
         <v>120</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L40" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M40" s="3">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -2571,8 +2904,16 @@
       <c r="J41" s="3">
         <v>107</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L41" s="3">
+        <f t="shared" si="4"/>
+        <v>185.4</v>
+      </c>
+      <c r="M41" s="3">
+        <f t="shared" si="5"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -2593,8 +2934,16 @@
       <c r="J42" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L42" s="3">
+        <f t="shared" si="4"/>
+        <v>827.52</v>
+      </c>
+      <c r="M42" s="3">
+        <f t="shared" si="5"/>
+        <v>960</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -2617,8 +2966,16 @@
       <c r="J43" s="3">
         <v>162</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L43" s="3">
+        <f t="shared" si="4"/>
+        <v>569.67999999999995</v>
+      </c>
+      <c r="M43" s="3">
+        <f t="shared" si="5"/>
+        <v>648</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>42</v>
       </c>
@@ -2641,8 +2998,16 @@
       <c r="J44" s="3">
         <v>56</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L44" s="3">
+        <f t="shared" si="4"/>
+        <v>1158.72</v>
+      </c>
+      <c r="M44" s="3">
+        <f t="shared" si="5"/>
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>43</v>
       </c>
@@ -2665,8 +3030,16 @@
       <c r="J45" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L45" s="3">
+        <f t="shared" si="4"/>
+        <v>2482.56</v>
+      </c>
+      <c r="M45" s="3">
+        <f t="shared" si="5"/>
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>44</v>
       </c>
@@ -2689,8 +3062,16 @@
       <c r="J46" s="3">
         <v>35</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L46" s="3">
+        <f t="shared" si="4"/>
+        <v>1358.1</v>
+      </c>
+      <c r="M46" s="3">
+        <f t="shared" si="5"/>
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45</v>
       </c>
@@ -2711,8 +3092,16 @@
       <c r="J47" s="3">
         <v>190</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L47" s="3">
+        <f t="shared" si="4"/>
+        <v>1965.48</v>
+      </c>
+      <c r="M47" s="3">
+        <f t="shared" si="5"/>
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>46</v>
       </c>
@@ -2733,8 +3122,16 @@
       <c r="J48" s="3">
         <v>160</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L48" s="3">
+        <f t="shared" si="4"/>
+        <v>965.43999999999994</v>
+      </c>
+      <c r="M48" s="3">
+        <f t="shared" si="5"/>
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>47</v>
       </c>
@@ -2757,8 +3154,16 @@
       <c r="J49" s="3">
         <v>302</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L49" s="3">
+        <f t="shared" si="4"/>
+        <v>834.8</v>
+      </c>
+      <c r="M49" s="3">
+        <f t="shared" si="5"/>
+        <v>604</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>48</v>
       </c>
@@ -2779,8 +3184,16 @@
       <c r="J50" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L50" s="3">
+        <f t="shared" si="4"/>
+        <v>867.75</v>
+      </c>
+      <c r="M50" s="3">
+        <f t="shared" si="5"/>
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>49</v>
       </c>
@@ -2803,8 +3216,16 @@
       <c r="J51" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L51" s="3">
+        <f t="shared" si="4"/>
+        <v>1903</v>
+      </c>
+      <c r="M51" s="3">
+        <f t="shared" si="5"/>
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>50</v>
       </c>
@@ -2825,8 +3246,16 @@
       <c r="J52" s="3">
         <v>230</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L52" s="3">
+        <f t="shared" si="4"/>
+        <v>990</v>
+      </c>
+      <c r="M52" s="3">
+        <f t="shared" si="5"/>
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>51</v>
       </c>
@@ -2849,8 +3278,16 @@
       <c r="J53" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L53" s="3">
+        <f t="shared" si="4"/>
+        <v>362.59999999999997</v>
+      </c>
+      <c r="M53" s="3">
+        <f t="shared" si="5"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>52</v>
       </c>
@@ -2869,8 +3306,16 @@
       <c r="J54" s="3">
         <v>343</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L54" s="3">
+        <f>E54*I54</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="3">
+        <f>E54*J54</f>
+        <v>686</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>53</v>
       </c>
@@ -2887,8 +3332,16 @@
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L55" s="3">
+        <f>E55*I55</f>
+        <v>0</v>
+      </c>
+      <c r="M55" s="3">
+        <f>E55*J55</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>54</v>
       </c>
@@ -2911,8 +3364,16 @@
       <c r="J56" s="3">
         <v>65</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L56" s="3">
+        <f t="shared" ref="L56" si="6">G56*I56</f>
+        <v>1905.02</v>
+      </c>
+      <c r="M56" s="3">
+        <f t="shared" ref="M56" si="7">G56*J56</f>
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>55</v>
       </c>
@@ -2933,8 +3394,16 @@
         <v>65</v>
       </c>
       <c r="J57" s="3"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L57" s="3">
+        <f t="shared" ref="L57:L63" si="8">G57*I57</f>
+        <v>1560</v>
+      </c>
+      <c r="M57" s="3">
+        <f t="shared" ref="M57:M63" si="9">G57*J57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>56</v>
       </c>
@@ -2955,8 +3424,16 @@
       <c r="J58" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L58" s="3">
+        <f t="shared" si="8"/>
+        <v>1723.5</v>
+      </c>
+      <c r="M58" s="3">
+        <f t="shared" si="9"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>57</v>
       </c>
@@ -2979,8 +3456,16 @@
       <c r="J59" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L59" s="3">
+        <f t="shared" si="8"/>
+        <v>879.75</v>
+      </c>
+      <c r="M59" s="3">
+        <f t="shared" si="9"/>
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>58</v>
       </c>
@@ -3001,8 +3486,16 @@
       <c r="J60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L60" s="3">
+        <f t="shared" si="8"/>
+        <v>3103.56</v>
+      </c>
+      <c r="M60" s="3">
+        <f t="shared" si="9"/>
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>59</v>
       </c>
@@ -3023,8 +3516,16 @@
       <c r="J61" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L61" s="3">
+        <f t="shared" si="8"/>
+        <v>1551.78</v>
+      </c>
+      <c r="M61" s="3">
+        <f t="shared" si="9"/>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>60</v>
       </c>
@@ -3047,8 +3548,16 @@
       <c r="J62" s="3">
         <v>90</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L62" s="3">
+        <f t="shared" si="8"/>
+        <v>1474.21</v>
+      </c>
+      <c r="M62" s="3">
+        <f t="shared" si="9"/>
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>61</v>
       </c>
@@ -3069,8 +3578,16 @@
       <c r="J63" s="3">
         <v>66</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L63" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <f t="shared" si="9"/>
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>62</v>
       </c>
@@ -3091,8 +3608,16 @@
       <c r="J64" s="3">
         <v>237.5</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L64" s="3">
+        <f>E64*I64</f>
+        <v>1638.25</v>
+      </c>
+      <c r="M64" s="3">
+        <f>E64*J64</f>
+        <v>1187.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>63</v>
       </c>
@@ -3111,8 +3636,16 @@
       <c r="J65" s="3">
         <v>210</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L65" s="3">
+        <f t="shared" ref="L65:L72" si="10">E65*I65</f>
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <f t="shared" ref="M65:M72" si="11">E65*J65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>64</v>
       </c>
@@ -3133,8 +3666,16 @@
       <c r="J66" s="3">
         <v>521</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L66" s="3">
+        <f t="shared" si="10"/>
+        <v>1583.06</v>
+      </c>
+      <c r="M66" s="3">
+        <f t="shared" si="11"/>
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>65</v>
       </c>
@@ -3155,8 +3696,16 @@
       <c r="J67" s="3">
         <v>218.76</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L67" s="3">
+        <f t="shared" si="10"/>
+        <v>1206.96</v>
+      </c>
+      <c r="M67" s="3">
+        <f t="shared" si="11"/>
+        <v>875.04</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>66</v>
       </c>
@@ -3177,8 +3726,16 @@
       <c r="J68" s="3">
         <v>176.98</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L68" s="3">
+        <f t="shared" si="10"/>
+        <v>244.1</v>
+      </c>
+      <c r="M68" s="3">
+        <f t="shared" si="11"/>
+        <v>176.98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>67</v>
       </c>
@@ -3199,8 +3756,16 @@
       <c r="J69" s="3">
         <v>69.010000000000005</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L69" s="3">
+        <f t="shared" si="10"/>
+        <v>96.01</v>
+      </c>
+      <c r="M69" s="3">
+        <f t="shared" si="11"/>
+        <v>69.010000000000005</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>68</v>
       </c>
@@ -3219,8 +3784,16 @@
       <c r="J70" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L70" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <f t="shared" si="11"/>
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>69</v>
       </c>
@@ -3241,8 +3814,16 @@
       <c r="J71" s="3">
         <v>320</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L71" s="3">
+        <f t="shared" si="10"/>
+        <v>350</v>
+      </c>
+      <c r="M71" s="3">
+        <f t="shared" si="11"/>
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>70</v>
       </c>
@@ -3263,8 +3844,16 @@
       <c r="J72" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L72" s="3">
+        <f t="shared" si="10"/>
+        <v>1666</v>
+      </c>
+      <c r="M72" s="3">
+        <f t="shared" si="11"/>
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>71</v>
       </c>
@@ -3287,8 +3876,16 @@
       <c r="J73" s="3">
         <v>19.2</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L73" s="3">
+        <f>G73*I73</f>
+        <v>120</v>
+      </c>
+      <c r="M73" s="3">
+        <f>G73*J73</f>
+        <v>76.8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>72</v>
       </c>
@@ -3309,8 +3906,16 @@
       <c r="J74" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L74" s="3">
+        <f t="shared" ref="L74" si="12">E74*I74</f>
+        <v>1185.7</v>
+      </c>
+      <c r="M74" s="3">
+        <f t="shared" ref="M74" si="13">E74*J74</f>
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>73</v>
       </c>
@@ -3332,8 +3937,16 @@
       <c r="J75" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L75" s="3">
+        <f t="shared" ref="L75:L80" si="14">E75*I75</f>
+        <v>270</v>
+      </c>
+      <c r="M75" s="3">
+        <f t="shared" ref="M75:M80" si="15">E75*J75</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>74</v>
       </c>
@@ -3354,8 +3967,16 @@
       <c r="J76" s="3">
         <v>65</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L76" s="3">
+        <f t="shared" si="14"/>
+        <v>400</v>
+      </c>
+      <c r="M76" s="3">
+        <f t="shared" si="15"/>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>75</v>
       </c>
@@ -3376,8 +3997,16 @@
       <c r="J77" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L77" s="3">
+        <f t="shared" si="14"/>
+        <v>342</v>
+      </c>
+      <c r="M77" s="3">
+        <f t="shared" si="15"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>76</v>
       </c>
@@ -3398,8 +4027,16 @@
       <c r="J78" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L78" s="3">
+        <f t="shared" si="14"/>
+        <v>210</v>
+      </c>
+      <c r="M78" s="3">
+        <f t="shared" si="15"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>77</v>
       </c>
@@ -3418,8 +4055,16 @@
       <c r="J79" s="3">
         <v>70</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L79" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M79" s="3">
+        <f t="shared" si="15"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>78</v>
       </c>
@@ -3438,8 +4083,16 @@
       <c r="J80" s="3">
         <v>320</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L80" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M80" s="3">
+        <f t="shared" si="15"/>
+        <v>960</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>79</v>
       </c>
@@ -3458,8 +4111,16 @@
       <c r="J81" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L81" s="3">
+        <f>G81*I81</f>
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
+        <f>G81*J81</f>
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>80</v>
       </c>
@@ -3478,8 +4139,16 @@
       <c r="J82" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L82" s="3">
+        <f>G82*I82</f>
+        <v>0</v>
+      </c>
+      <c r="M82" s="3">
+        <f>G82*J82</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>81</v>
       </c>
@@ -3498,8 +4167,16 @@
       <c r="J83" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L83" s="3">
+        <f t="shared" ref="L83:L136" si="16">G83*I83</f>
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <f t="shared" ref="M83:M136" si="17">G83*J83</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>82</v>
       </c>
@@ -3520,8 +4197,16 @@
       <c r="J84" s="3">
         <v>160</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L84" s="3">
+        <f t="shared" si="16"/>
+        <v>5517.2000000000007</v>
+      </c>
+      <c r="M84" s="3">
+        <f t="shared" si="17"/>
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>83</v>
       </c>
@@ -3542,8 +4227,16 @@
       <c r="J85" s="3">
         <v>187.5</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L85" s="3">
+        <f t="shared" si="16"/>
+        <v>2910.2400000000002</v>
+      </c>
+      <c r="M85" s="3">
+        <f t="shared" si="17"/>
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>84</v>
       </c>
@@ -3564,8 +4257,16 @@
       <c r="J86" s="3">
         <v>34.5</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L86" s="3">
+        <f t="shared" si="16"/>
+        <v>208.25</v>
+      </c>
+      <c r="M86" s="3">
+        <f t="shared" si="17"/>
+        <v>241.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>85</v>
       </c>
@@ -3586,8 +4287,16 @@
       <c r="J87" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L87" s="3">
+        <f t="shared" si="16"/>
+        <v>323.75</v>
+      </c>
+      <c r="M87" s="3">
+        <f t="shared" si="17"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>86</v>
       </c>
@@ -3606,8 +4315,16 @@
       <c r="J88" s="3">
         <v>90</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L88" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <f t="shared" si="17"/>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>87</v>
       </c>
@@ -3628,8 +4345,16 @@
       <c r="J89" s="3">
         <v>120</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L89" s="3">
+        <f t="shared" si="16"/>
+        <v>1034.5999999999999</v>
+      </c>
+      <c r="M89" s="3">
+        <f t="shared" si="17"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>88</v>
       </c>
@@ -3650,8 +4375,16 @@
       <c r="J90" s="3">
         <v>97.5</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L90" s="3">
+        <f t="shared" si="16"/>
+        <v>840.5</v>
+      </c>
+      <c r="M90" s="3">
+        <f t="shared" si="17"/>
+        <v>975</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>89</v>
       </c>
@@ -3672,8 +4405,16 @@
       <c r="J91" s="3">
         <v>130</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L91" s="3">
+        <f t="shared" si="16"/>
+        <v>1014.3000000000001</v>
+      </c>
+      <c r="M91" s="3">
+        <f t="shared" si="17"/>
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>90</v>
       </c>
@@ -3696,8 +4437,16 @@
       <c r="J92" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L92" s="3">
+        <f t="shared" si="16"/>
+        <v>3228.64</v>
+      </c>
+      <c r="M92" s="3">
+        <f t="shared" si="17"/>
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>91</v>
       </c>
@@ -3718,8 +4467,16 @@
       <c r="J93" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L93" s="3">
+        <f t="shared" si="16"/>
+        <v>517.28</v>
+      </c>
+      <c r="M93" s="3">
+        <f t="shared" si="17"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>92</v>
       </c>
@@ -3740,8 +4497,16 @@
       <c r="J94" s="3">
         <v>34.5</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L94" s="3">
+        <f t="shared" si="16"/>
+        <v>297.5</v>
+      </c>
+      <c r="M94" s="3">
+        <f t="shared" si="17"/>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>93</v>
       </c>
@@ -3762,8 +4527,16 @@
       <c r="J95" s="3">
         <v>187.5</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L95" s="3">
+        <f t="shared" si="16"/>
+        <v>4202.38</v>
+      </c>
+      <c r="M95" s="3">
+        <f t="shared" si="17"/>
+        <v>4875</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>94</v>
       </c>
@@ -3784,8 +4557,16 @@
       <c r="J96" s="3">
         <v>97.5</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L96" s="3">
+        <f t="shared" si="16"/>
+        <v>840.5</v>
+      </c>
+      <c r="M96" s="3">
+        <f t="shared" si="17"/>
+        <v>975</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>95</v>
       </c>
@@ -3806,8 +4587,16 @@
       <c r="J97" s="3">
         <v>27.5</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L97" s="3">
+        <f t="shared" si="16"/>
+        <v>664.71999999999991</v>
+      </c>
+      <c r="M97" s="3">
+        <f t="shared" si="17"/>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>96</v>
       </c>
@@ -3828,8 +4617,16 @@
       <c r="J98" s="3">
         <v>114</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L98" s="3">
+        <f t="shared" si="16"/>
+        <v>983</v>
+      </c>
+      <c r="M98" s="3">
+        <f t="shared" si="17"/>
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>97</v>
       </c>
@@ -3850,8 +4647,16 @@
       <c r="J99" s="3">
         <v>105</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L99" s="3">
+        <f t="shared" si="16"/>
+        <v>905.19999999999993</v>
+      </c>
+      <c r="M99" s="3">
+        <f t="shared" si="17"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>98</v>
       </c>
@@ -3872,8 +4677,16 @@
       <c r="J100" s="3">
         <v>130</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L100" s="3">
+        <f t="shared" si="16"/>
+        <v>1354.32</v>
+      </c>
+      <c r="M100" s="3">
+        <f t="shared" si="17"/>
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>99</v>
       </c>
@@ -3894,8 +4707,16 @@
       <c r="J101" s="3">
         <v>114</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L101" s="3">
+        <f t="shared" si="16"/>
+        <v>1376.2</v>
+      </c>
+      <c r="M101" s="3">
+        <f t="shared" si="17"/>
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>100</v>
       </c>
@@ -3916,8 +4737,16 @@
       <c r="J102" s="3">
         <v>27.56</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L102" s="3">
+        <f t="shared" si="16"/>
+        <v>228.60000000000002</v>
+      </c>
+      <c r="M102" s="3">
+        <f t="shared" si="17"/>
+        <v>165.35999999999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>101</v>
       </c>
@@ -3938,8 +4767,16 @@
       <c r="J103" s="3">
         <v>119</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L103" s="3">
+        <f t="shared" si="16"/>
+        <v>165.68</v>
+      </c>
+      <c r="M103" s="3">
+        <f t="shared" si="17"/>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>102</v>
       </c>
@@ -3960,8 +4797,16 @@
       <c r="J104" s="3">
         <v>47.5</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L104" s="3">
+        <f t="shared" si="16"/>
+        <v>1247.73</v>
+      </c>
+      <c r="M104" s="3">
+        <f t="shared" si="17"/>
+        <v>902.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>103</v>
       </c>
@@ -3980,8 +4825,16 @@
       <c r="J105" s="3">
         <v>79.64</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L105" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M105" s="3">
+        <f t="shared" si="17"/>
+        <v>318.56</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>104</v>
       </c>
@@ -4002,8 +4855,16 @@
       <c r="J106" s="3">
         <v>160</v>
       </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L106" s="3">
+        <f t="shared" si="16"/>
+        <v>1379.8</v>
+      </c>
+      <c r="M106" s="3">
+        <f t="shared" si="17"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>105</v>
       </c>
@@ -4024,8 +4885,16 @@
       <c r="J107" s="3">
         <v>132.5</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L107" s="3">
+        <f t="shared" si="16"/>
+        <v>1644.84</v>
+      </c>
+      <c r="M107" s="3">
+        <f t="shared" si="17"/>
+        <v>1192.5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>106</v>
       </c>
@@ -4046,8 +4915,16 @@
       <c r="J108" s="3">
         <v>82.99</v>
       </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L108" s="3">
+        <f t="shared" si="16"/>
+        <v>549.5</v>
+      </c>
+      <c r="M108" s="3">
+        <f t="shared" si="17"/>
+        <v>414.95</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>107</v>
       </c>
@@ -4066,8 +4943,16 @@
       <c r="J109" s="3">
         <v>114</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L109" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M109" s="3">
+        <f t="shared" si="17"/>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>108</v>
       </c>
@@ -4088,8 +4973,16 @@
       <c r="J110" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L110" s="3">
+        <f t="shared" si="16"/>
+        <v>2586.1999999999998</v>
+      </c>
+      <c r="M110" s="3">
+        <f t="shared" si="17"/>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -4100,8 +4993,16 @@
       <c r="H111" s="3"/>
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L111" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M111" s="3">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>109</v>
       </c>
@@ -4120,8 +5021,16 @@
       <c r="J112" s="3">
         <v>247</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L112" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M112" s="3">
+        <f t="shared" si="17"/>
+        <v>741</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>110</v>
       </c>
@@ -4142,8 +5051,16 @@
       <c r="J113" s="3">
         <v>132.5</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L113" s="3">
+        <f t="shared" si="16"/>
+        <v>365.52</v>
+      </c>
+      <c r="M113" s="3">
+        <f t="shared" si="17"/>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>111</v>
       </c>
@@ -4166,8 +5083,16 @@
       <c r="J114" s="3">
         <v>141.43</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L114" s="3">
+        <f t="shared" si="16"/>
+        <v>1365.3500000000001</v>
+      </c>
+      <c r="M114" s="3">
+        <f t="shared" si="17"/>
+        <v>990.01</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>112</v>
       </c>
@@ -4188,8 +5113,16 @@
       <c r="J115" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L115" s="3">
+        <f t="shared" si="16"/>
+        <v>60.480000000000004</v>
+      </c>
+      <c r="M115" s="3">
+        <f t="shared" si="17"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>113</v>
       </c>
@@ -4210,8 +5143,16 @@
       <c r="J116" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L116" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M116" s="3">
+        <f t="shared" si="17"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>114</v>
       </c>
@@ -4234,8 +5175,16 @@
       <c r="J117" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L117" s="3">
+        <f t="shared" si="16"/>
+        <v>758.56</v>
+      </c>
+      <c r="M117" s="3">
+        <f t="shared" si="17"/>
+        <v>880</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>115</v>
       </c>
@@ -4258,8 +5207,16 @@
       <c r="J118" s="3">
         <v>84</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L118" s="3">
+        <f t="shared" si="16"/>
+        <v>146.02000000000001</v>
+      </c>
+      <c r="M118" s="3">
+        <f t="shared" si="17"/>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>116</v>
       </c>
@@ -4280,8 +5237,16 @@
       <c r="J119" s="3">
         <v>350</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L119" s="3">
+        <f t="shared" si="16"/>
+        <v>4525.8</v>
+      </c>
+      <c r="M119" s="3">
+        <f t="shared" si="17"/>
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>117</v>
       </c>
@@ -4302,8 +5267,16 @@
       <c r="J120" s="3">
         <v>110</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L120" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M120" s="3">
+        <f t="shared" si="17"/>
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>118</v>
       </c>
@@ -4322,8 +5295,16 @@
       <c r="J121" s="3">
         <v>375</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L121" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M121" s="3">
+        <f t="shared" si="17"/>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>119</v>
       </c>
@@ -4346,8 +5327,16 @@
       <c r="J122" s="3">
         <v>120</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L122" s="3">
+        <f t="shared" si="16"/>
+        <v>620.81999999999994</v>
+      </c>
+      <c r="M122" s="3">
+        <f t="shared" si="17"/>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
         <v>120</v>
       </c>
@@ -4368,8 +5357,16 @@
       <c r="J123" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L123" s="3">
+        <f t="shared" si="16"/>
+        <v>1724.95</v>
+      </c>
+      <c r="M123" s="3">
+        <f t="shared" si="17"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
         <v>121</v>
       </c>
@@ -4390,8 +5387,16 @@
       <c r="J124" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L124" s="3">
+        <f t="shared" si="16"/>
+        <v>1896.73</v>
+      </c>
+      <c r="M124" s="3">
+        <f t="shared" si="17"/>
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
         <v>122</v>
       </c>
@@ -4412,8 +5417,16 @@
       <c r="J125" s="3">
         <v>13.5</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L125" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M125" s="3">
+        <f t="shared" si="17"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
         <v>123</v>
       </c>
@@ -4432,8 +5445,16 @@
       <c r="J126" s="3">
         <v>550</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L126" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M126" s="3">
+        <f t="shared" si="17"/>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
         <v>124</v>
       </c>
@@ -4454,8 +5475,16 @@
       <c r="J127" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L127" s="3">
+        <f t="shared" si="16"/>
+        <v>17.239999999999998</v>
+      </c>
+      <c r="M127" s="3">
+        <f t="shared" si="17"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
         <v>125</v>
       </c>
@@ -4476,8 +5505,16 @@
       <c r="J128" s="3">
         <v>37.5</v>
       </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L128" s="3">
+        <f t="shared" si="16"/>
+        <v>226.38000000000002</v>
+      </c>
+      <c r="M128" s="3">
+        <f t="shared" si="17"/>
+        <v>262.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
         <v>126</v>
       </c>
@@ -4498,8 +5535,16 @@
       <c r="J129" s="3">
         <v>375</v>
       </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L129" s="3">
+        <f t="shared" si="16"/>
+        <v>1939.6799999999998</v>
+      </c>
+      <c r="M129" s="3">
+        <f t="shared" si="17"/>
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
         <v>127</v>
       </c>
@@ -4520,8 +5565,16 @@
       <c r="J130" s="3">
         <v>34</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L130" s="3">
+        <f t="shared" si="16"/>
+        <v>1031.58</v>
+      </c>
+      <c r="M130" s="3">
+        <f t="shared" si="17"/>
+        <v>748</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
         <v>128</v>
       </c>
@@ -4542,8 +5595,16 @@
       <c r="J131" s="3">
         <v>37.5</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L131" s="3">
+        <f t="shared" si="16"/>
+        <v>711.26</v>
+      </c>
+      <c r="M131" s="3">
+        <f t="shared" si="17"/>
+        <v>825</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
         <v>129</v>
       </c>
@@ -4562,8 +5623,16 @@
       <c r="J132" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L132" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M132" s="3">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
         <v>130</v>
       </c>
@@ -4580,8 +5649,16 @@
       <c r="H133" s="3"/>
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L133" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M133" s="3">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
         <v>131</v>
       </c>
@@ -4602,8 +5679,16 @@
       <c r="J134" s="3">
         <v>270</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L134" s="3">
+        <f t="shared" si="16"/>
+        <v>698.40000000000009</v>
+      </c>
+      <c r="M134" s="3">
+        <f t="shared" si="17"/>
+        <v>810</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
         <v>132</v>
       </c>
@@ -4622,8 +5707,16 @@
       <c r="J135" s="3">
         <v>260</v>
       </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L135" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M135" s="3">
+        <f t="shared" si="17"/>
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
         <v>133</v>
       </c>
@@ -4644,8 +5737,16 @@
       <c r="J136" s="3">
         <v>260</v>
       </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L136" s="3">
+        <f t="shared" si="16"/>
+        <v>1120.8</v>
+      </c>
+      <c r="M136" s="3">
+        <f t="shared" si="17"/>
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
         <v>134</v>
       </c>
@@ -4666,8 +5767,16 @@
       <c r="J137" s="3">
         <v>90</v>
       </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L137" s="3">
+        <f>E137*I137</f>
+        <v>155.19999999999999</v>
+      </c>
+      <c r="M137" s="3">
+        <f>E137*J137</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
         <v>135</v>
       </c>
@@ -4688,8 +5797,16 @@
       <c r="J138" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L138" s="3">
+        <f>E138*I138</f>
+        <v>948.19999999999993</v>
+      </c>
+      <c r="M138" s="3">
+        <f>E138*J138</f>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -4700,8 +5817,10 @@
       <c r="H139" s="3"/>
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L139" s="3"/>
+      <c r="M139" s="3"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>136</v>
       </c>
@@ -4722,8 +5841,16 @@
       <c r="J140" s="3">
         <v>28</v>
       </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L140" s="3">
+        <f>E140*I140</f>
+        <v>131.12</v>
+      </c>
+      <c r="M140" s="3">
+        <f>E140*J140</f>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
         <v>137</v>
       </c>
@@ -4744,8 +5871,16 @@
       <c r="J141" s="3">
         <v>105.9</v>
       </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L141" s="3">
+        <f t="shared" ref="L141:L151" si="18">E141*I141</f>
+        <v>438.21</v>
+      </c>
+      <c r="M141" s="3">
+        <f t="shared" ref="M141:M151" si="19">E141*J141</f>
+        <v>317.70000000000005</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
         <v>138</v>
       </c>
@@ -4766,8 +5901,16 @@
       <c r="J142" s="3">
         <v>63.91</v>
       </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L142" s="3">
+        <f t="shared" si="18"/>
+        <v>264.45000000000005</v>
+      </c>
+      <c r="M142" s="3">
+        <f t="shared" si="19"/>
+        <v>191.73</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
         <v>139</v>
       </c>
@@ -4788,8 +5931,16 @@
       <c r="J143" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L143" s="3">
+        <f t="shared" si="18"/>
+        <v>517.77</v>
+      </c>
+      <c r="M143" s="3">
+        <f t="shared" si="19"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
         <v>140</v>
       </c>
@@ -4808,8 +5959,16 @@
       <c r="J144" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L144" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="M144" s="3">
+        <f t="shared" si="19"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
         <v>141</v>
       </c>
@@ -4830,8 +5989,16 @@
       <c r="J145" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L145" s="3">
+        <f t="shared" si="18"/>
+        <v>862.09999999999991</v>
+      </c>
+      <c r="M145" s="3">
+        <f t="shared" si="19"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
         <v>142</v>
       </c>
@@ -4852,8 +6019,16 @@
       <c r="J146" s="3">
         <v>141.43</v>
       </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L146" s="3">
+        <f t="shared" si="18"/>
+        <v>1566.8</v>
+      </c>
+      <c r="M146" s="3">
+        <f t="shared" si="19"/>
+        <v>1131.44</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="3">
         <v>143</v>
       </c>
@@ -4874,8 +6049,16 @@
       <c r="J147" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L147" s="3">
+        <f t="shared" si="18"/>
+        <v>1379.36</v>
+      </c>
+      <c r="M147" s="3">
+        <f t="shared" si="19"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
         <v>144</v>
       </c>
@@ -4896,8 +6079,16 @@
       <c r="J148" s="3">
         <v>250</v>
       </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L148" s="3">
+        <f t="shared" si="18"/>
+        <v>860</v>
+      </c>
+      <c r="M148" s="3">
+        <f t="shared" si="19"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="3">
         <v>145</v>
       </c>
@@ -4918,8 +6109,16 @@
       <c r="J149" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L149" s="3">
+        <f t="shared" si="18"/>
+        <v>155.10000000000002</v>
+      </c>
+      <c r="M149" s="3">
+        <f t="shared" si="19"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
         <v>146</v>
       </c>
@@ -4940,8 +6139,16 @@
       <c r="J150" s="3">
         <v>77</v>
       </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L150" s="3">
+        <f t="shared" si="18"/>
+        <v>1194.8399999999999</v>
+      </c>
+      <c r="M150" s="3">
+        <f t="shared" si="19"/>
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="3">
         <v>147</v>
       </c>
@@ -4962,8 +6169,16 @@
       <c r="J151" s="3">
         <v>137.63999999999999</v>
       </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L151" s="3">
+        <f t="shared" si="18"/>
+        <v>569.61</v>
+      </c>
+      <c r="M151" s="3">
+        <f t="shared" si="19"/>
+        <v>412.91999999999996</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
         <v>148</v>
       </c>
@@ -4984,8 +6199,16 @@
       <c r="J152" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L152" s="3">
+        <f t="shared" ref="L152" si="20">G152*I152</f>
+        <v>315</v>
+      </c>
+      <c r="M152" s="3">
+        <f t="shared" ref="M152" si="21">G152*J152</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
         <v>149</v>
       </c>
@@ -5006,8 +6229,16 @@
       <c r="J153" s="3">
         <v>155</v>
       </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L153" s="3">
+        <f t="shared" ref="L153" si="22">E153*I153</f>
+        <v>1068.96</v>
+      </c>
+      <c r="M153" s="3">
+        <f t="shared" ref="M153" si="23">E153*J153</f>
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>150</v>
       </c>
@@ -5028,8 +6259,16 @@
       <c r="J154" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L154" s="3">
+        <f t="shared" ref="L154:L166" si="24">E154*I154</f>
+        <v>344.82</v>
+      </c>
+      <c r="M154" s="3">
+        <f t="shared" ref="M154:M166" si="25">E154*J154</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
         <v>151</v>
       </c>
@@ -5048,8 +6287,16 @@
       <c r="J155" s="3">
         <v>195</v>
       </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L155" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="M155" s="3">
+        <f t="shared" si="25"/>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
         <v>152</v>
       </c>
@@ -5070,8 +6317,16 @@
       <c r="J156" s="3">
         <v>220</v>
       </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L156" s="3">
+        <f t="shared" si="24"/>
+        <v>189.65</v>
+      </c>
+      <c r="M156" s="3">
+        <f t="shared" si="25"/>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="3">
         <v>153</v>
       </c>
@@ -5092,8 +6347,16 @@
       <c r="J157" s="3">
         <v>280.86</v>
       </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L157" s="3">
+        <f t="shared" si="24"/>
+        <v>774.78</v>
+      </c>
+      <c r="M157" s="3">
+        <f t="shared" si="25"/>
+        <v>561.72</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
         <v>154</v>
       </c>
@@ -5114,8 +6377,16 @@
       <c r="J158" s="3">
         <v>189.72</v>
       </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L158" s="3">
+        <f t="shared" si="24"/>
+        <v>523.36</v>
+      </c>
+      <c r="M158" s="3">
+        <f t="shared" si="25"/>
+        <v>379.44</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="3">
         <v>155</v>
       </c>
@@ -5136,8 +6407,16 @@
       <c r="J159" s="3">
         <v>185.4</v>
       </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L159" s="3">
+        <f t="shared" si="24"/>
+        <v>767.18999999999994</v>
+      </c>
+      <c r="M159" s="3">
+        <f t="shared" si="25"/>
+        <v>556.20000000000005</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
         <v>156</v>
       </c>
@@ -5158,8 +6437,16 @@
       <c r="J160" s="3">
         <v>140.83000000000001</v>
       </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L160" s="3">
+        <f t="shared" si="24"/>
+        <v>582.75</v>
+      </c>
+      <c r="M160" s="3">
+        <f t="shared" si="25"/>
+        <v>422.49</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="3">
         <v>157</v>
       </c>
@@ -5180,8 +6467,16 @@
       <c r="J161" s="3">
         <v>183.97</v>
       </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L161" s="3">
+        <f t="shared" si="24"/>
+        <v>511.5</v>
+      </c>
+      <c r="M161" s="3">
+        <f t="shared" si="25"/>
+        <v>367.94</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
         <v>158</v>
       </c>
@@ -5202,8 +6497,16 @@
       <c r="J162" s="3">
         <v>168.83</v>
       </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L162" s="3">
+        <f t="shared" si="24"/>
+        <v>465.72</v>
+      </c>
+      <c r="M162" s="3">
+        <f t="shared" si="25"/>
+        <v>337.66</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="3">
         <v>159</v>
       </c>
@@ -5224,8 +6527,16 @@
       <c r="J163" s="3">
         <v>150</v>
       </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L163" s="3">
+        <f t="shared" si="24"/>
+        <v>129.30000000000001</v>
+      </c>
+      <c r="M163" s="3">
+        <f t="shared" si="25"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
         <v>160</v>
       </c>
@@ -5244,8 +6555,16 @@
       <c r="J164" s="3">
         <v>71.5</v>
       </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L164" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="M164" s="3">
+        <f t="shared" si="25"/>
+        <v>214.5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="3">
         <v>161</v>
       </c>
@@ -5264,8 +6583,16 @@
       <c r="J165" s="3">
         <v>148</v>
       </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L165" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="M165" s="3">
+        <f t="shared" si="25"/>
+        <v>592</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
         <v>162</v>
       </c>
@@ -5284,8 +6611,16 @@
       <c r="J166" s="3">
         <v>130.69999999999999</v>
       </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L166" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="M166" s="3">
+        <f t="shared" si="25"/>
+        <v>392.09999999999997</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -5296,8 +6631,10 @@
       <c r="H167" s="3"/>
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L167" s="3"/>
+      <c r="M167" s="3"/>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
         <v>163</v>
       </c>
@@ -5318,8 +6655,16 @@
       <c r="J168" s="3">
         <v>320</v>
       </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L168" s="3">
+        <f t="shared" ref="L168" si="26">E168*I168</f>
+        <v>1655.16</v>
+      </c>
+      <c r="M168" s="3">
+        <f t="shared" ref="M168" si="27">E168*J168</f>
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" s="3">
         <v>164</v>
       </c>
@@ -5340,8 +6685,16 @@
       <c r="J169" s="3">
         <v>104</v>
       </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L169" s="3">
+        <f t="shared" ref="L169:L215" si="28">E169*I169</f>
+        <v>1256.5</v>
+      </c>
+      <c r="M169" s="3">
+        <f t="shared" ref="M169:M215" si="29">E169*J169</f>
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" s="3">
         <v>165</v>
       </c>
@@ -5360,8 +6713,16 @@
       <c r="J170" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L170" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M170" s="3">
+        <f t="shared" si="29"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="3">
         <v>166</v>
       </c>
@@ -5382,8 +6743,16 @@
       <c r="J171" s="3">
         <v>185</v>
       </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L171" s="3">
+        <f t="shared" si="28"/>
+        <v>1277.1500000000001</v>
+      </c>
+      <c r="M171" s="3">
+        <f t="shared" si="29"/>
+        <v>925</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" s="3">
         <v>167</v>
       </c>
@@ -5404,8 +6773,16 @@
       <c r="J172" s="3">
         <v>130</v>
       </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L172" s="3">
+        <f t="shared" si="28"/>
+        <v>784.49</v>
+      </c>
+      <c r="M172" s="3">
+        <f t="shared" si="29"/>
+        <v>910</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="3">
         <v>168</v>
       </c>
@@ -5426,8 +6803,16 @@
       <c r="J173" s="3">
         <v>130</v>
       </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L173" s="3">
+        <f t="shared" si="28"/>
+        <v>224.12</v>
+      </c>
+      <c r="M173" s="3">
+        <f t="shared" si="29"/>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
         <v>169</v>
       </c>
@@ -5448,8 +6833,16 @@
       <c r="J174" s="3">
         <v>165</v>
       </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L174" s="3">
+        <f t="shared" si="28"/>
+        <v>571.12</v>
+      </c>
+      <c r="M174" s="3">
+        <f t="shared" si="29"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="3">
         <v>170</v>
       </c>
@@ -5470,8 +6863,16 @@
       <c r="J175" s="3">
         <v>320</v>
       </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L175" s="3">
+        <f t="shared" si="28"/>
+        <v>551.72</v>
+      </c>
+      <c r="M175" s="3">
+        <f t="shared" si="29"/>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
         <v>171</v>
       </c>
@@ -5492,8 +6893,16 @@
       <c r="J176" s="3">
         <v>110</v>
       </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L176" s="3">
+        <f t="shared" si="28"/>
+        <v>2584</v>
+      </c>
+      <c r="M176" s="3">
+        <f t="shared" si="29"/>
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
         <v>172</v>
       </c>
@@ -5514,8 +6923,16 @@
       <c r="J177" s="3">
         <v>110</v>
       </c>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L177" s="3">
+        <f t="shared" si="28"/>
+        <v>760</v>
+      </c>
+      <c r="M177" s="3">
+        <f t="shared" si="29"/>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>173</v>
       </c>
@@ -5536,8 +6953,16 @@
       <c r="J178" s="3">
         <v>130</v>
       </c>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L178" s="3">
+        <f t="shared" si="28"/>
+        <v>4281.84</v>
+      </c>
+      <c r="M178" s="3">
+        <f t="shared" si="29"/>
+        <v>4940</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
         <v>174</v>
       </c>
@@ -5558,8 +6983,16 @@
       <c r="J179" s="3">
         <v>96</v>
       </c>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L179" s="3">
+        <f t="shared" si="28"/>
+        <v>248.34</v>
+      </c>
+      <c r="M179" s="3">
+        <f t="shared" si="29"/>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>175</v>
       </c>
@@ -5580,8 +7013,16 @@
       <c r="J180" s="3">
         <v>175</v>
       </c>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L180" s="3">
+        <f t="shared" si="28"/>
+        <v>1064</v>
+      </c>
+      <c r="M180" s="3">
+        <f t="shared" si="29"/>
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" s="3">
         <v>176</v>
       </c>
@@ -5600,8 +7041,16 @@
       <c r="J181" s="3">
         <v>320</v>
       </c>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L181" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M181" s="3">
+        <f t="shared" si="29"/>
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" s="3">
         <v>177</v>
       </c>
@@ -5620,8 +7069,16 @@
       <c r="J182" s="3">
         <v>117</v>
       </c>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L182" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M182" s="3">
+        <f t="shared" si="29"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="3">
         <v>178</v>
       </c>
@@ -5642,8 +7099,16 @@
       <c r="J183" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L183" s="3">
+        <f t="shared" si="28"/>
+        <v>672</v>
+      </c>
+      <c r="M183" s="3">
+        <f t="shared" si="29"/>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="3">
         <v>179</v>
       </c>
@@ -5664,8 +7129,16 @@
       <c r="J184" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L184" s="3">
+        <f t="shared" si="28"/>
+        <v>520</v>
+      </c>
+      <c r="M184" s="3">
+        <f t="shared" si="29"/>
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="3">
         <v>180</v>
       </c>
@@ -5686,8 +7159,16 @@
       <c r="J185" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L185" s="3">
+        <f t="shared" si="28"/>
+        <v>207.12</v>
+      </c>
+      <c r="M185" s="3">
+        <f t="shared" si="29"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
         <v>181</v>
       </c>
@@ -5708,8 +7189,16 @@
       <c r="J186" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L186" s="3">
+        <f t="shared" si="28"/>
+        <v>775.98</v>
+      </c>
+      <c r="M186" s="3">
+        <f t="shared" si="29"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="3">
         <v>182</v>
       </c>
@@ -5728,8 +7217,16 @@
       <c r="J187" s="3">
         <v>135</v>
       </c>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L187" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M187" s="3">
+        <f t="shared" si="29"/>
+        <v>810</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
         <v>183</v>
       </c>
@@ -5748,8 +7245,16 @@
       <c r="J188" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L188" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M188" s="3">
+        <f t="shared" si="29"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="3">
         <v>184</v>
       </c>
@@ -5770,8 +7275,16 @@
       <c r="J189" s="3">
         <v>77</v>
       </c>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L189" s="3">
+        <f t="shared" si="28"/>
+        <v>265.52</v>
+      </c>
+      <c r="M189" s="3">
+        <f t="shared" si="29"/>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="3">
         <v>185</v>
       </c>
@@ -5792,8 +7305,16 @@
       <c r="J190" s="3">
         <v>105</v>
       </c>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L190" s="3">
+        <f t="shared" si="28"/>
+        <v>1086.1200000000001</v>
+      </c>
+      <c r="M190" s="3">
+        <f t="shared" si="29"/>
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" s="3">
         <v>186</v>
       </c>
@@ -5812,8 +7333,16 @@
       <c r="J191" s="3">
         <v>99</v>
       </c>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L191" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M191" s="3">
+        <f t="shared" si="29"/>
+        <v>396</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
         <v>187</v>
       </c>
@@ -5834,8 +7363,16 @@
       <c r="J192" s="3">
         <v>110</v>
       </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L192" s="3">
+        <f t="shared" si="28"/>
+        <v>758.8</v>
+      </c>
+      <c r="M192" s="3">
+        <f t="shared" si="29"/>
+        <v>880</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" s="3">
         <v>188</v>
       </c>
@@ -5848,8 +7385,16 @@
       <c r="H193" s="3"/>
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L193" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M193" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="3">
         <v>189</v>
       </c>
@@ -5870,8 +7415,16 @@
       <c r="J194" s="3">
         <v>105</v>
       </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L194" s="3">
+        <f t="shared" si="28"/>
+        <v>999.34999999999991</v>
+      </c>
+      <c r="M194" s="3">
+        <f t="shared" si="29"/>
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" s="3">
         <v>190</v>
       </c>
@@ -5892,8 +7445,16 @@
       <c r="J195" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L195" s="3">
+        <f t="shared" si="28"/>
+        <v>897</v>
+      </c>
+      <c r="M195" s="3">
+        <f t="shared" si="29"/>
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
         <v>191</v>
       </c>
@@ -5912,8 +7473,16 @@
       <c r="J196" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L196" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M196" s="3">
+        <f t="shared" si="29"/>
+        <v>825</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" s="3">
         <v>192</v>
       </c>
@@ -5934,8 +7503,16 @@
       <c r="J197" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L197" s="3">
+        <f t="shared" si="28"/>
+        <v>362.32</v>
+      </c>
+      <c r="M197" s="3">
+        <f t="shared" si="29"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" s="3">
         <v>193</v>
       </c>
@@ -5956,8 +7533,16 @@
       <c r="J198" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L198" s="3">
+        <f t="shared" si="28"/>
+        <v>772.52</v>
+      </c>
+      <c r="M198" s="3">
+        <f t="shared" si="29"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" s="3">
         <v>194</v>
       </c>
@@ -5978,8 +7563,16 @@
       <c r="J199" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L199" s="3">
+        <f t="shared" si="28"/>
+        <v>206.96</v>
+      </c>
+      <c r="M199" s="3">
+        <f t="shared" si="29"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
         <v>195</v>
       </c>
@@ -6000,8 +7593,16 @@
       <c r="J200" s="3">
         <v>320</v>
       </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L200" s="3">
+        <f t="shared" si="28"/>
+        <v>855</v>
+      </c>
+      <c r="M200" s="3">
+        <f t="shared" si="29"/>
+        <v>960</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" s="3">
         <v>196</v>
       </c>
@@ -6022,8 +7623,16 @@
       <c r="J201" s="3">
         <v>41</v>
       </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L201" s="3">
+        <f t="shared" si="28"/>
+        <v>60</v>
+      </c>
+      <c r="M201" s="3">
+        <f t="shared" si="29"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" s="3">
         <v>197</v>
       </c>
@@ -6044,8 +7653,16 @@
       <c r="J202" s="3">
         <v>83</v>
       </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L202" s="3">
+        <f t="shared" si="28"/>
+        <v>256</v>
+      </c>
+      <c r="M202" s="3">
+        <f t="shared" si="29"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" s="3">
         <v>198</v>
       </c>
@@ -6066,8 +7683,16 @@
       <c r="J203" s="3">
         <v>220</v>
       </c>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L203" s="3">
+        <f t="shared" si="28"/>
+        <v>390</v>
+      </c>
+      <c r="M203" s="3">
+        <f t="shared" si="29"/>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" s="3">
         <v>199</v>
       </c>
@@ -6086,8 +7711,16 @@
       <c r="J204" s="3">
         <v>250</v>
       </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L204" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M204" s="3">
+        <f t="shared" si="29"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" s="3">
         <v>200</v>
       </c>
@@ -6108,8 +7741,16 @@
       <c r="J205" s="3">
         <v>1500</v>
       </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L205" s="3">
+        <f t="shared" si="28"/>
+        <v>785</v>
+      </c>
+      <c r="M205" s="3">
+        <f t="shared" si="29"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" s="3">
         <v>201</v>
       </c>
@@ -6130,8 +7771,16 @@
       <c r="J206" s="3">
         <v>250</v>
       </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L206" s="3">
+        <f t="shared" si="28"/>
+        <v>250</v>
+      </c>
+      <c r="M206" s="3">
+        <f t="shared" si="29"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207" s="3">
         <v>202</v>
       </c>
@@ -6152,8 +7801,16 @@
       <c r="J207" s="3">
         <v>250</v>
       </c>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L207" s="3">
+        <f t="shared" si="28"/>
+        <v>125</v>
+      </c>
+      <c r="M207" s="3">
+        <f t="shared" si="29"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" s="3">
         <v>203</v>
       </c>
@@ -6174,8 +7831,16 @@
       <c r="J208" s="3">
         <v>175</v>
       </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L208" s="3">
+        <f t="shared" si="28"/>
+        <v>840</v>
+      </c>
+      <c r="M208" s="3">
+        <f t="shared" si="29"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" s="3">
         <v>204</v>
       </c>
@@ -6196,8 +7861,16 @@
       <c r="J209" s="3">
         <v>110</v>
       </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L209" s="3">
+        <f t="shared" si="28"/>
+        <v>85</v>
+      </c>
+      <c r="M209" s="3">
+        <f t="shared" si="29"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210" s="3">
         <v>205</v>
       </c>
@@ -6218,8 +7891,16 @@
       <c r="J210" s="3">
         <v>425</v>
       </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L210" s="3">
+        <f t="shared" si="28"/>
+        <v>195</v>
+      </c>
+      <c r="M210" s="3">
+        <f t="shared" si="29"/>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211" s="3">
         <v>206</v>
       </c>
@@ -6240,8 +7921,16 @@
       <c r="J211" s="3">
         <v>190</v>
       </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L211" s="3">
+        <f t="shared" si="28"/>
+        <v>1188</v>
+      </c>
+      <c r="M211" s="3">
+        <f t="shared" si="29"/>
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212" s="3">
         <v>207</v>
       </c>
@@ -6260,8 +7949,16 @@
       <c r="J212" s="3">
         <v>137</v>
       </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L212" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M212" s="3">
+        <f t="shared" si="29"/>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" s="3">
         <v>208</v>
       </c>
@@ -6280,8 +7977,16 @@
       <c r="J213" s="3">
         <v>87.5</v>
       </c>
-    </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L213" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M213" s="3">
+        <f t="shared" si="29"/>
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" s="3">
         <v>209</v>
       </c>
@@ -6302,8 +8007,16 @@
       <c r="J214" s="3">
         <v>245</v>
       </c>
-    </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L214" s="3">
+        <f t="shared" si="28"/>
+        <v>341</v>
+      </c>
+      <c r="M214" s="3">
+        <f t="shared" si="29"/>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" s="3">
         <v>210</v>
       </c>
@@ -6324,8 +8037,16 @@
       <c r="J215" s="3">
         <v>135</v>
       </c>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L215" s="3">
+        <f t="shared" si="28"/>
+        <v>549</v>
+      </c>
+      <c r="M215" s="3">
+        <f t="shared" si="29"/>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" s="3">
         <v>211</v>
       </c>
@@ -6338,8 +8059,10 @@
       <c r="H216" s="3"/>
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L216" s="3"/>
+      <c r="M216" s="3"/>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" s="3">
         <v>212</v>
       </c>
@@ -6352,8 +8075,10 @@
       <c r="H217" s="3"/>
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
-    </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L217" s="3"/>
+      <c r="M217" s="3"/>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" s="3">
         <v>213</v>
       </c>
@@ -6366,8 +8091,10 @@
       <c r="H218" s="3"/>
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L218" s="3"/>
+      <c r="M218" s="3"/>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" s="3">
         <v>214</v>
       </c>
@@ -6380,8 +8107,10 @@
       <c r="H219" s="3"/>
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L219" s="3"/>
+      <c r="M219" s="3"/>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220" s="3">
         <v>215</v>
       </c>
@@ -6394,8 +8123,10 @@
       <c r="H220" s="3"/>
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L220" s="3"/>
+      <c r="M220" s="3"/>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" s="3">
         <v>216</v>
       </c>
@@ -6408,8 +8139,10 @@
       <c r="H221" s="3"/>
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L221" s="3"/>
+      <c r="M221" s="3"/>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" s="3">
         <v>217</v>
       </c>
@@ -6422,8 +8155,10 @@
       <c r="H222" s="3"/>
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L222" s="3"/>
+      <c r="M222" s="3"/>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" s="3">
         <v>218</v>
       </c>
@@ -6436,8 +8171,10 @@
       <c r="H223" s="3"/>
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
-    </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L223" s="3"/>
+      <c r="M223" s="3"/>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" s="3">
         <v>219</v>
       </c>
@@ -6450,8 +8187,10 @@
       <c r="H224" s="3"/>
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L224" s="3"/>
+      <c r="M224" s="3"/>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" s="3">
         <v>220</v>
       </c>
@@ -6464,8 +8203,10 @@
       <c r="H225" s="3"/>
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L225" s="3"/>
+      <c r="M225" s="3"/>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" s="3">
         <v>221</v>
       </c>
@@ -6486,8 +8227,16 @@
       <c r="J226" s="3">
         <v>85</v>
       </c>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L226" s="3">
+        <f t="shared" ref="L226" si="30">E226*I226</f>
+        <v>230</v>
+      </c>
+      <c r="M226" s="3">
+        <f t="shared" ref="M226" si="31">E226*J226</f>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" s="3">
         <v>222</v>
       </c>
@@ -6506,8 +8255,16 @@
       <c r="J227" s="3">
         <v>79.2</v>
       </c>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L227" s="3">
+        <f t="shared" ref="L227:L290" si="32">E227*I227</f>
+        <v>0</v>
+      </c>
+      <c r="M227" s="3">
+        <f t="shared" ref="M227:M290" si="33">E227*J227</f>
+        <v>633.6</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" s="3">
         <v>223</v>
       </c>
@@ -6526,8 +8283,16 @@
       <c r="J228" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L228" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M228" s="3">
+        <f t="shared" si="33"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" s="3">
         <v>224</v>
       </c>
@@ -6548,8 +8313,16 @@
       <c r="J229" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L229" s="3">
+        <f t="shared" si="32"/>
+        <v>180</v>
+      </c>
+      <c r="M229" s="3">
+        <f t="shared" si="33"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" s="3">
         <v>225</v>
       </c>
@@ -6568,8 +8341,16 @@
       <c r="J230" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L230" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M230" s="3">
+        <f t="shared" si="33"/>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" s="3">
         <v>226</v>
       </c>
@@ -6590,8 +8371,16 @@
       <c r="J231" s="3">
         <v>85</v>
       </c>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L231" s="3">
+        <f t="shared" si="32"/>
+        <v>941.32999999999993</v>
+      </c>
+      <c r="M231" s="3">
+        <f t="shared" si="33"/>
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" s="3">
         <v>227</v>
       </c>
@@ -6612,8 +8401,16 @@
       <c r="J232" s="3">
         <v>18</v>
       </c>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L232" s="3">
+        <f t="shared" si="32"/>
+        <v>93.12</v>
+      </c>
+      <c r="M232" s="3">
+        <f t="shared" si="33"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
         <v>228</v>
       </c>
@@ -6634,8 +8431,16 @@
       <c r="J233" s="3">
         <v>143</v>
       </c>
-    </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L233" s="3">
+        <f t="shared" si="32"/>
+        <v>592.56000000000006</v>
+      </c>
+      <c r="M233" s="3">
+        <f t="shared" si="33"/>
+        <v>429</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234" s="3">
         <v>229</v>
       </c>
@@ -6656,8 +8461,16 @@
       <c r="J234" s="3">
         <v>135</v>
       </c>
-    </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L234" s="3">
+        <f t="shared" si="32"/>
+        <v>466.68</v>
+      </c>
+      <c r="M234" s="3">
+        <f t="shared" si="33"/>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" s="3">
         <v>230</v>
       </c>
@@ -6678,8 +8491,16 @@
       <c r="J235" s="3">
         <v>95</v>
       </c>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L235" s="3">
+        <f t="shared" si="32"/>
+        <v>410</v>
+      </c>
+      <c r="M235" s="3">
+        <f t="shared" si="33"/>
+        <v>475</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236" s="3">
         <v>231</v>
       </c>
@@ -6700,8 +8521,16 @@
       <c r="J236" s="3">
         <v>102</v>
       </c>
-    </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L236" s="3">
+        <f t="shared" si="32"/>
+        <v>281.36</v>
+      </c>
+      <c r="M236" s="3">
+        <f t="shared" si="33"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237" s="3">
         <v>232</v>
       </c>
@@ -6722,8 +8551,16 @@
       <c r="J237" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L237" s="3">
+        <f t="shared" si="32"/>
+        <v>155.28</v>
+      </c>
+      <c r="M237" s="3">
+        <f t="shared" si="33"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238" s="3">
         <v>233</v>
       </c>
@@ -6744,8 +8581,16 @@
       <c r="J238" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L238" s="3">
+        <f t="shared" si="32"/>
+        <v>284.52</v>
+      </c>
+      <c r="M238" s="3">
+        <f t="shared" si="33"/>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239" s="3">
         <v>234</v>
       </c>
@@ -6766,8 +8611,16 @@
       <c r="J239" s="3">
         <v>145</v>
       </c>
-    </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L239" s="3">
+        <f t="shared" si="32"/>
+        <v>625.05000000000007</v>
+      </c>
+      <c r="M239" s="3">
+        <f t="shared" si="33"/>
+        <v>725</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" s="3">
         <v>235</v>
       </c>
@@ -6788,8 +8641,16 @@
       <c r="J240" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L240" s="3">
+        <f t="shared" si="32"/>
+        <v>195</v>
+      </c>
+      <c r="M240" s="3">
+        <f t="shared" si="33"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A241" s="3">
         <v>236</v>
       </c>
@@ -6810,8 +8671,16 @@
       <c r="J241" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L241" s="3">
+        <f t="shared" si="32"/>
+        <v>290</v>
+      </c>
+      <c r="M241" s="3">
+        <f t="shared" si="33"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A242" s="3">
         <v>237</v>
       </c>
@@ -6832,8 +8701,16 @@
       <c r="J242" s="3">
         <v>150</v>
       </c>
-    </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L242" s="3">
+        <f t="shared" si="32"/>
+        <v>560</v>
+      </c>
+      <c r="M242" s="3">
+        <f t="shared" si="33"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243" s="3">
         <v>238</v>
       </c>
@@ -6854,8 +8731,16 @@
       <c r="J243" s="3">
         <v>260</v>
       </c>
-    </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L243" s="3">
+        <f t="shared" si="32"/>
+        <v>650</v>
+      </c>
+      <c r="M243" s="3">
+        <f t="shared" si="33"/>
+        <v>520</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244" s="3">
         <v>239</v>
       </c>
@@ -6876,8 +8761,16 @@
       <c r="J244" s="3">
         <v>525</v>
       </c>
-    </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L244" s="3">
+        <f t="shared" si="32"/>
+        <v>740</v>
+      </c>
+      <c r="M244" s="3">
+        <f t="shared" si="33"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A245" s="3">
         <v>240</v>
       </c>
@@ -6896,8 +8789,16 @@
       <c r="J245" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L245" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M245" s="3">
+        <f t="shared" si="33"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A246" s="3">
         <v>241</v>
       </c>
@@ -6918,8 +8819,16 @@
       <c r="J246" s="3">
         <v>65</v>
       </c>
-    </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L246" s="3">
+        <f t="shared" si="32"/>
+        <v>160</v>
+      </c>
+      <c r="M246" s="3">
+        <f t="shared" si="33"/>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247" s="3">
         <v>242</v>
       </c>
@@ -6938,8 +8847,16 @@
       <c r="J247" s="3">
         <v>220</v>
       </c>
-    </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L247" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M247" s="3">
+        <f t="shared" si="33"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248" s="3">
         <v>243</v>
       </c>
@@ -6958,8 +8875,16 @@
       <c r="J248" s="3">
         <v>320</v>
       </c>
-    </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L248" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M248" s="3">
+        <f t="shared" si="33"/>
+        <v>960</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A249" s="3">
         <v>244</v>
       </c>
@@ -6980,8 +8905,16 @@
       <c r="J249" s="3">
         <v>48</v>
       </c>
-    </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L249" s="3">
+        <f t="shared" si="32"/>
+        <v>198.60000000000002</v>
+      </c>
+      <c r="M249" s="3">
+        <f t="shared" si="33"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A250" s="3">
         <v>245</v>
       </c>
@@ -7002,8 +8935,16 @@
       <c r="J250" s="3">
         <v>120</v>
       </c>
-    </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L250" s="3">
+        <f t="shared" si="32"/>
+        <v>406.71</v>
+      </c>
+      <c r="M250" s="3">
+        <f t="shared" si="33"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A251" s="3">
         <v>246</v>
       </c>
@@ -7024,8 +8965,16 @@
       <c r="J251" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L251" s="3">
+        <f t="shared" si="32"/>
+        <v>350</v>
+      </c>
+      <c r="M251" s="3">
+        <f t="shared" si="33"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A252" s="3">
         <v>247</v>
       </c>
@@ -7046,8 +8995,16 @@
       <c r="J252" s="3">
         <v>175</v>
       </c>
-    </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L252" s="3">
+        <f t="shared" si="32"/>
+        <v>300</v>
+      </c>
+      <c r="M252" s="3">
+        <f t="shared" si="33"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A253" s="3">
         <v>248</v>
       </c>
@@ -7068,8 +9025,16 @@
       <c r="J253" s="3">
         <v>85</v>
       </c>
-    </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L253" s="3">
+        <f t="shared" si="32"/>
+        <v>805.96999999999991</v>
+      </c>
+      <c r="M253" s="3">
+        <f t="shared" si="33"/>
+        <v>935</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A254" s="3">
         <v>249</v>
       </c>
@@ -7090,8 +9055,16 @@
       <c r="J254" s="3">
         <v>129</v>
       </c>
-    </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L254" s="3">
+        <f t="shared" si="32"/>
+        <v>711.72</v>
+      </c>
+      <c r="M254" s="3">
+        <f t="shared" si="33"/>
+        <v>516</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A255" s="3">
         <v>250</v>
       </c>
@@ -7112,8 +9085,16 @@
       <c r="J255" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L255" s="3">
+        <f t="shared" si="32"/>
+        <v>552</v>
+      </c>
+      <c r="M255" s="3">
+        <f t="shared" si="33"/>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A256" s="3">
         <v>251</v>
       </c>
@@ -7134,8 +9115,16 @@
       <c r="J256" s="3">
         <v>173.5</v>
       </c>
-    </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L256" s="3">
+        <f t="shared" si="32"/>
+        <v>1437.1200000000001</v>
+      </c>
+      <c r="M256" s="3">
+        <f t="shared" si="33"/>
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A257" s="3">
         <v>252</v>
       </c>
@@ -7156,8 +9145,16 @@
       <c r="J257" s="3">
         <v>120</v>
       </c>
-    </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L257" s="3">
+        <f t="shared" si="32"/>
+        <v>993.12000000000012</v>
+      </c>
+      <c r="M257" s="3">
+        <f t="shared" si="33"/>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A258" s="3">
         <v>253</v>
       </c>
@@ -7178,8 +9175,16 @@
       <c r="J258" s="3">
         <v>159</v>
       </c>
-    </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L258" s="3">
+        <f t="shared" si="32"/>
+        <v>5507.6</v>
+      </c>
+      <c r="M258" s="3">
+        <f t="shared" si="33"/>
+        <v>6360</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A259" s="3">
         <v>254</v>
       </c>
@@ -7200,8 +9205,16 @@
       <c r="J259" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L259" s="3">
+        <f t="shared" si="32"/>
+        <v>4310.4000000000005</v>
+      </c>
+      <c r="M259" s="3">
+        <f t="shared" si="33"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
         <v>255</v>
       </c>
@@ -7222,8 +9235,16 @@
       <c r="J260" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L260" s="3">
+        <f t="shared" si="32"/>
+        <v>905.10000000000014</v>
+      </c>
+      <c r="M260" s="3">
+        <f t="shared" si="33"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A261" s="3">
         <v>256</v>
       </c>
@@ -7244,8 +9265,16 @@
       <c r="J261" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L261" s="3">
+        <f t="shared" si="32"/>
+        <v>862.05</v>
+      </c>
+      <c r="M261" s="3">
+        <f t="shared" si="33"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A262" s="3">
         <v>257</v>
       </c>
@@ -7266,8 +9295,16 @@
       <c r="J262" s="3">
         <v>250</v>
       </c>
-    </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L262" s="3">
+        <f t="shared" si="32"/>
+        <v>1290</v>
+      </c>
+      <c r="M262" s="3">
+        <f t="shared" si="33"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A263" s="3">
         <v>258</v>
       </c>
@@ -7288,8 +9325,16 @@
       <c r="J263" s="3">
         <v>250</v>
       </c>
-    </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L263" s="3">
+        <f t="shared" si="32"/>
+        <v>220</v>
+      </c>
+      <c r="M263" s="3">
+        <f t="shared" si="33"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A264" s="3">
         <v>259</v>
       </c>
@@ -7310,8 +9355,16 @@
       <c r="J264" s="3">
         <v>110</v>
       </c>
-    </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L264" s="3">
+        <f t="shared" si="32"/>
+        <v>474.09999999999997</v>
+      </c>
+      <c r="M264" s="3">
+        <f t="shared" si="33"/>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A265" s="3">
         <v>260</v>
       </c>
@@ -7326,8 +9379,16 @@
       <c r="H265" s="3"/>
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
-    </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L265" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M265" s="3">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A266" s="3">
         <v>261</v>
       </c>
@@ -7348,8 +9409,16 @@
       <c r="J266" s="3">
         <v>145</v>
       </c>
-    </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L266" s="3">
+        <f t="shared" si="32"/>
+        <v>750</v>
+      </c>
+      <c r="M266" s="3">
+        <f t="shared" si="33"/>
+        <v>870</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A267" s="3">
         <v>262</v>
       </c>
@@ -7370,8 +9439,16 @@
       <c r="J267" s="3">
         <v>95</v>
       </c>
-    </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L267" s="3">
+        <f t="shared" si="32"/>
+        <v>573.23</v>
+      </c>
+      <c r="M267" s="3">
+        <f t="shared" si="33"/>
+        <v>665</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A268" s="3">
         <v>263</v>
       </c>
@@ -7390,8 +9467,16 @@
       <c r="J268" s="3">
         <v>143</v>
       </c>
-    </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L268" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M268" s="3">
+        <f t="shared" si="33"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A269" s="3">
         <v>264</v>
       </c>
@@ -7410,8 +9495,16 @@
       <c r="J269" s="3">
         <v>160</v>
       </c>
-    </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L269" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M269" s="3">
+        <f t="shared" si="33"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A270" s="3">
         <v>265</v>
       </c>
@@ -7432,8 +9525,16 @@
       <c r="J270" s="3">
         <v>302</v>
       </c>
-    </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L270" s="3">
+        <f t="shared" si="32"/>
+        <v>520</v>
+      </c>
+      <c r="M270" s="3">
+        <f t="shared" si="33"/>
+        <v>604</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A271" s="3">
         <v>266</v>
       </c>
@@ -7454,8 +9555,16 @@
       <c r="J271" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L271" s="3">
+        <f t="shared" si="32"/>
+        <v>1980</v>
+      </c>
+      <c r="M271" s="3">
+        <f t="shared" si="33"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A272" s="3">
         <v>267</v>
       </c>
@@ -7476,8 +9585,16 @@
       <c r="J272" s="3">
         <v>290</v>
       </c>
-    </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L272" s="3">
+        <f t="shared" si="32"/>
+        <v>530</v>
+      </c>
+      <c r="M272" s="3">
+        <f t="shared" si="33"/>
+        <v>580</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A273" s="3">
         <v>268</v>
       </c>
@@ -7498,8 +9615,16 @@
       <c r="J273" s="3">
         <v>175</v>
       </c>
-    </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L273" s="3">
+        <f t="shared" si="32"/>
+        <v>450</v>
+      </c>
+      <c r="M273" s="3">
+        <f t="shared" si="33"/>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A274" s="3">
         <v>269</v>
       </c>
@@ -7520,8 +9645,16 @@
       <c r="J274" s="3">
         <v>90</v>
       </c>
-    </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L274" s="3">
+        <f t="shared" si="32"/>
+        <v>672</v>
+      </c>
+      <c r="M274" s="3">
+        <f t="shared" si="33"/>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A275" s="3">
         <v>270</v>
       </c>
@@ -7542,8 +9675,16 @@
       <c r="J275" s="3">
         <v>140</v>
       </c>
-    </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L275" s="3">
+        <f t="shared" si="32"/>
+        <v>350</v>
+      </c>
+      <c r="M275" s="3">
+        <f t="shared" si="33"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A276" s="3">
         <v>271</v>
       </c>
@@ -7562,8 +9703,16 @@
       <c r="J276" s="3">
         <v>175</v>
       </c>
-    </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L276" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M276" s="3">
+        <f t="shared" si="33"/>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A277" s="3">
         <v>272</v>
       </c>
@@ -7582,8 +9731,16 @@
       <c r="J277" s="3">
         <v>105</v>
       </c>
-    </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L277" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M277" s="3">
+        <f t="shared" si="33"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A278" s="3">
         <v>273</v>
       </c>
@@ -7604,8 +9761,16 @@
       <c r="J278" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L278" s="3">
+        <f t="shared" si="32"/>
+        <v>949</v>
+      </c>
+      <c r="M278" s="3">
+        <f t="shared" si="33"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A279" s="3">
         <v>274</v>
       </c>
@@ -7626,8 +9791,16 @@
       <c r="J279" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L279" s="3">
+        <f t="shared" si="32"/>
+        <v>172.42</v>
+      </c>
+      <c r="M279" s="3">
+        <f t="shared" si="33"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A280" s="3">
         <v>275</v>
       </c>
@@ -7648,8 +9821,16 @@
       <c r="J280" s="3">
         <v>70</v>
       </c>
-    </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L280" s="3">
+        <f t="shared" si="32"/>
+        <v>1689.8</v>
+      </c>
+      <c r="M280" s="3">
+        <f t="shared" si="33"/>
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A281" s="3">
         <v>276</v>
       </c>
@@ -7670,8 +9851,16 @@
       <c r="J281" s="3">
         <v>150</v>
       </c>
-    </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L281" s="3">
+        <f t="shared" si="32"/>
+        <v>4020.0800000000004</v>
+      </c>
+      <c r="M281" s="3">
+        <f t="shared" si="33"/>
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A282" s="3">
         <v>277</v>
       </c>
@@ -7692,8 +9881,16 @@
       <c r="J282" s="3">
         <v>130</v>
       </c>
-    </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L282" s="3">
+        <f t="shared" si="32"/>
+        <v>3042.36</v>
+      </c>
+      <c r="M282" s="3">
+        <f t="shared" si="33"/>
+        <v>3510</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A283" s="3">
         <v>278</v>
       </c>
@@ -7714,8 +9911,16 @@
       <c r="J283" s="3">
         <v>70</v>
       </c>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L283" s="3">
+        <f t="shared" si="32"/>
+        <v>422.45</v>
+      </c>
+      <c r="M283" s="3">
+        <f t="shared" si="33"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A284" s="3">
         <v>279</v>
       </c>
@@ -7734,8 +9939,16 @@
       <c r="J284" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L284" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M284" s="3">
+        <f t="shared" si="33"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A285" s="3">
         <v>280</v>
       </c>
@@ -7756,8 +9969,16 @@
       <c r="J285" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L285" s="3">
+        <f t="shared" si="32"/>
+        <v>300</v>
+      </c>
+      <c r="M285" s="3">
+        <f t="shared" si="33"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A286" s="3">
         <v>281</v>
       </c>
@@ -7776,8 +9997,16 @@
       <c r="J286" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L286" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M286" s="3">
+        <f t="shared" si="33"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A287" s="4">
         <v>282</v>
       </c>
@@ -7798,8 +10027,16 @@
       <c r="J287" s="3">
         <v>110</v>
       </c>
-    </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L287" s="3">
+        <f t="shared" si="32"/>
+        <v>196</v>
+      </c>
+      <c r="M287" s="3">
+        <f t="shared" si="33"/>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A288" s="3">
         <v>283</v>
       </c>
@@ -7820,8 +10057,16 @@
       <c r="J288" s="3">
         <v>125</v>
       </c>
-    </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L288" s="3">
+        <f t="shared" si="32"/>
+        <v>936</v>
+      </c>
+      <c r="M288" s="3">
+        <f t="shared" si="33"/>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A289" s="3">
         <v>284</v>
       </c>
@@ -7840,8 +10085,16 @@
       <c r="J289" s="3">
         <v>105</v>
       </c>
-    </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L289" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M289" s="3">
+        <f t="shared" si="33"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A290" s="3">
         <v>285</v>
       </c>
@@ -7860,8 +10113,16 @@
       <c r="J290" s="3">
         <v>175</v>
       </c>
-    </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L290" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M290" s="3">
+        <f t="shared" si="33"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A291" s="3">
         <v>286</v>
       </c>
@@ -7882,8 +10143,16 @@
       <c r="J291" s="3">
         <v>106</v>
       </c>
-    </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L291" s="3">
+        <f t="shared" ref="L291:L315" si="34">E291*I291</f>
+        <v>660</v>
+      </c>
+      <c r="M291" s="3">
+        <f t="shared" ref="M291:M315" si="35">E291*J291</f>
+        <v>530</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A292" s="3">
         <v>287</v>
       </c>
@@ -7904,8 +10173,16 @@
       <c r="J292" s="3">
         <v>115</v>
       </c>
-    </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L292" s="3">
+        <f t="shared" si="34"/>
+        <v>144</v>
+      </c>
+      <c r="M292" s="3">
+        <f t="shared" si="35"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A293" s="3">
         <v>288</v>
       </c>
@@ -7924,8 +10201,16 @@
       <c r="J293" s="3">
         <v>65</v>
       </c>
-    </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L293" s="3">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="M293" s="3">
+        <f t="shared" si="35"/>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A294" s="3">
         <v>289</v>
       </c>
@@ -7944,8 +10229,16 @@
       <c r="J294" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L294" s="3">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="M294" s="3">
+        <f t="shared" si="35"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A295" s="3">
         <v>290</v>
       </c>
@@ -7964,8 +10257,16 @@
       <c r="J295" s="3">
         <v>120</v>
       </c>
-    </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L295" s="3">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="M295" s="3">
+        <f t="shared" si="35"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A296" s="3">
         <v>291</v>
       </c>
@@ -7984,8 +10285,16 @@
       <c r="J296" s="3">
         <v>70</v>
       </c>
-    </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L296" s="3">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="M296" s="3">
+        <f t="shared" si="35"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A297" s="3">
         <v>292</v>
       </c>
@@ -8004,8 +10313,16 @@
       <c r="J297" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L297" s="3">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="M297" s="3">
+        <f t="shared" si="35"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A298" s="3">
         <v>293</v>
       </c>
@@ -8026,8 +10343,16 @@
       <c r="J298" s="3">
         <v>890</v>
       </c>
-    </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L298" s="3">
+        <f t="shared" si="34"/>
+        <v>810</v>
+      </c>
+      <c r="M298" s="3">
+        <f t="shared" si="35"/>
+        <v>890</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A299" s="3">
         <v>294</v>
       </c>
@@ -8048,8 +10373,16 @@
       <c r="J299" s="3">
         <v>890</v>
       </c>
-    </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L299" s="3">
+        <f t="shared" si="34"/>
+        <v>810</v>
+      </c>
+      <c r="M299" s="3">
+        <f t="shared" si="35"/>
+        <v>890</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A300" s="3">
         <v>295</v>
       </c>
@@ -8070,8 +10403,16 @@
       <c r="J300" s="3">
         <v>898</v>
       </c>
-    </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L300" s="3">
+        <f t="shared" si="34"/>
+        <v>1634</v>
+      </c>
+      <c r="M300" s="3">
+        <f t="shared" si="35"/>
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A301" s="3">
         <v>296</v>
       </c>
@@ -8092,8 +10433,16 @@
       <c r="J301" s="3">
         <v>896</v>
       </c>
-    </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L301" s="3">
+        <f t="shared" si="34"/>
+        <v>1632</v>
+      </c>
+      <c r="M301" s="3">
+        <f t="shared" si="35"/>
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A302" s="3">
         <v>297</v>
       </c>
@@ -8114,8 +10463,16 @@
       <c r="J302" s="3">
         <v>526</v>
       </c>
-    </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L302" s="3">
+        <f t="shared" si="34"/>
+        <v>480</v>
+      </c>
+      <c r="M302" s="3">
+        <f t="shared" si="35"/>
+        <v>526</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A303" s="3">
         <v>298</v>
       </c>
@@ -8136,8 +10493,16 @@
       <c r="J303" s="3">
         <v>552</v>
       </c>
-    </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L303" s="3">
+        <f t="shared" si="34"/>
+        <v>501</v>
+      </c>
+      <c r="M303" s="3">
+        <f t="shared" si="35"/>
+        <v>552</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A304" s="3">
         <v>299</v>
       </c>
@@ -8158,8 +10523,16 @@
       <c r="J304" s="3">
         <v>544</v>
       </c>
-    </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L304" s="3">
+        <f t="shared" si="34"/>
+        <v>994</v>
+      </c>
+      <c r="M304" s="3">
+        <f t="shared" si="35"/>
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A305" s="3">
         <v>300</v>
       </c>
@@ -8180,8 +10553,16 @@
       <c r="J305" s="3">
         <v>571</v>
       </c>
-    </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L305" s="3">
+        <f t="shared" si="34"/>
+        <v>519</v>
+      </c>
+      <c r="M305" s="3">
+        <f t="shared" si="35"/>
+        <v>571</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A306" s="3">
         <v>301</v>
       </c>
@@ -8202,8 +10583,16 @@
       <c r="J306" s="3">
         <v>580</v>
       </c>
-    </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L306" s="3">
+        <f t="shared" si="34"/>
+        <v>531</v>
+      </c>
+      <c r="M306" s="3">
+        <f t="shared" si="35"/>
+        <v>580</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A307" s="3">
         <v>302</v>
       </c>
@@ -8222,8 +10611,16 @@
       <c r="J307" s="3">
         <v>59</v>
       </c>
-    </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L307" s="3">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="M307" s="3">
+        <f t="shared" si="35"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A308" s="3"/>
       <c r="B308" s="3" t="s">
         <v>294</v>
@@ -8240,8 +10637,16 @@
       <c r="J308" s="3">
         <v>59</v>
       </c>
-    </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L308" s="3">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="M308" s="3">
+        <f t="shared" si="35"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A309" s="3">
         <v>303</v>
       </c>
@@ -8260,8 +10665,16 @@
       <c r="J309" s="3">
         <v>99</v>
       </c>
-    </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L309" s="3">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="M309" s="3">
+        <f t="shared" si="35"/>
+        <v>297</v>
+      </c>
+    </row>
+    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A310" s="3">
         <v>304</v>
       </c>
@@ -8282,8 +10695,16 @@
       <c r="J310" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L310" s="3">
+        <f t="shared" si="34"/>
+        <v>870</v>
+      </c>
+      <c r="M310" s="3">
+        <f t="shared" si="35"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A311" s="3">
         <v>305</v>
       </c>
@@ -8304,8 +10725,16 @@
       <c r="J311" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L311" s="3">
+        <f t="shared" si="34"/>
+        <v>1280</v>
+      </c>
+      <c r="M311" s="3">
+        <f t="shared" si="35"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A312" s="3">
         <v>306</v>
       </c>
@@ -8326,8 +10755,16 @@
       <c r="J312" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L312" s="3">
+        <f t="shared" si="34"/>
+        <v>266</v>
+      </c>
+      <c r="M312" s="3">
+        <f t="shared" si="35"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A313" s="3">
         <v>307</v>
       </c>
@@ -8348,8 +10785,16 @@
       <c r="J313" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L313" s="3">
+        <f t="shared" si="34"/>
+        <v>91</v>
+      </c>
+      <c r="M313" s="3">
+        <f t="shared" si="35"/>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A314" s="3">
         <v>308</v>
       </c>
@@ -8370,8 +10815,16 @@
       <c r="J314" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L314" s="3">
+        <f t="shared" si="34"/>
+        <v>1575</v>
+      </c>
+      <c r="M314" s="3">
+        <f t="shared" si="35"/>
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A315" s="4">
         <v>309</v>
       </c>
@@ -8390,8 +10843,16 @@
       <c r="J315" s="3">
         <v>110</v>
       </c>
-    </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L315" s="3">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="M315" s="3">
+        <f t="shared" si="35"/>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A316" s="3">
         <v>310</v>
       </c>
@@ -8403,15 +10864,22 @@
       <c r="E316" s="3"/>
       <c r="F316" s="3"/>
       <c r="G316" s="3"/>
-      <c r="H316" s="3">
+      <c r="I316" s="3">
         <v>135</v>
       </c>
-      <c r="I316" s="3">
+      <c r="J316" s="3">
         <v>200</v>
       </c>
-      <c r="J316" s="3"/>
-    </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L316" s="3">
+        <f t="shared" ref="L316" si="36">E316*I316</f>
+        <v>0</v>
+      </c>
+      <c r="M316" s="3">
+        <f t="shared" ref="M316" si="37">E316*J316</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A317" s="3">
         <v>311</v>
       </c>
@@ -8432,8 +10900,16 @@
       <c r="J317" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L317" s="3">
+        <f>G317*I317</f>
+        <v>1534</v>
+      </c>
+      <c r="M317" s="3">
+        <f>G317*J317</f>
+        <v>4720</v>
+      </c>
+    </row>
+    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A318" s="3">
         <v>312</v>
       </c>
@@ -8454,8 +10930,16 @@
       <c r="J318" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L318" s="3">
+        <f t="shared" ref="L318" si="38">E318*I318</f>
+        <v>1420</v>
+      </c>
+      <c r="M318" s="3">
+        <f t="shared" ref="M318" si="39">E318*J318</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A319" s="3">
         <v>313</v>
       </c>
@@ -8476,8 +10960,16 @@
       <c r="J319" s="3">
         <v>85</v>
       </c>
-    </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L319" s="3">
+        <f t="shared" ref="L319" si="40">E319*I319</f>
+        <v>711</v>
+      </c>
+      <c r="M319" s="3">
+        <f t="shared" ref="M319" si="41">E319*J319</f>
+        <v>765</v>
+      </c>
+    </row>
+    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A320" s="3">
         <v>314</v>
       </c>
@@ -8500,8 +10992,16 @@
       <c r="J320" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L320" s="3">
+        <f>G320*I320</f>
+        <v>1248</v>
+      </c>
+      <c r="M320" s="3">
+        <f>G320*J320</f>
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A321" s="3">
         <v>315</v>
       </c>
@@ -8520,8 +11020,16 @@
       <c r="J321" s="3">
         <v>112</v>
       </c>
-    </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L321" s="3">
+        <f t="shared" ref="L321:L323" si="42">G321*I321</f>
+        <v>0</v>
+      </c>
+      <c r="M321" s="3">
+        <f t="shared" ref="M321:M323" si="43">G321*J321</f>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A322" s="3">
         <v>316</v>
       </c>
@@ -8542,8 +11050,16 @@
       <c r="J322" s="3">
         <v>180</v>
       </c>
-    </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L322" s="3">
+        <f t="shared" si="42"/>
+        <v>1870.1999999999998</v>
+      </c>
+      <c r="M322" s="3">
+        <f t="shared" si="43"/>
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A323" s="3">
         <v>317</v>
       </c>
@@ -8566,8 +11082,16 @@
       <c r="J323" s="3">
         <v>180</v>
       </c>
-    </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L323" s="3">
+        <f t="shared" si="42"/>
+        <v>1551.8000000000002</v>
+      </c>
+      <c r="M323" s="3">
+        <f t="shared" si="43"/>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A324" s="3">
         <v>318</v>
       </c>
@@ -8586,8 +11110,16 @@
       <c r="J324" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L324" s="3">
+        <f t="shared" ref="L324" si="44">E324*I324</f>
+        <v>0</v>
+      </c>
+      <c r="M324" s="3">
+        <f t="shared" ref="M324" si="45">E324*J324</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A325" s="3">
         <v>319</v>
       </c>
@@ -8606,8 +11138,16 @@
       <c r="J325" s="3">
         <v>95</v>
       </c>
-    </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L325" s="3">
+        <f t="shared" ref="L325" si="46">E325*I325</f>
+        <v>0</v>
+      </c>
+      <c r="M325" s="3">
+        <f t="shared" ref="M325" si="47">E325*J325</f>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A326" s="3">
         <v>320</v>
       </c>
@@ -8628,8 +11168,16 @@
       <c r="J326" s="3">
         <v>56</v>
       </c>
-    </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L326" s="3">
+        <f t="shared" ref="L326" si="48">G326*I326</f>
+        <v>0</v>
+      </c>
+      <c r="M326" s="3">
+        <f t="shared" ref="M326" si="49">G326*J326</f>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A327" s="3">
         <v>321</v>
       </c>
@@ -8648,8 +11196,16 @@
       <c r="J327" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L327" s="3">
+        <f t="shared" ref="L327:L336" si="50">G327*I327</f>
+        <v>0</v>
+      </c>
+      <c r="M327" s="3">
+        <f t="shared" ref="M327:M336" si="51">G327*J327</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A328" s="3">
         <v>322</v>
       </c>
@@ -8668,8 +11224,16 @@
       <c r="J328" s="3">
         <v>140</v>
       </c>
-    </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L328" s="3">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="M328" s="3">
+        <f t="shared" si="51"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A329" s="3">
         <v>323</v>
       </c>
@@ -8688,8 +11252,16 @@
       <c r="J329" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L329" s="3">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="M329" s="3">
+        <f t="shared" si="51"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A330" s="3">
         <v>324</v>
       </c>
@@ -8708,8 +11280,16 @@
       <c r="J330" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L330" s="3">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="M330" s="3">
+        <f t="shared" si="51"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A331" s="3">
         <v>325</v>
       </c>
@@ -8728,8 +11308,16 @@
       <c r="J331" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L331" s="3">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="M331" s="3">
+        <f t="shared" si="51"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A332" s="3">
         <v>326</v>
       </c>
@@ -8748,8 +11336,16 @@
       <c r="J332" s="3">
         <v>314</v>
       </c>
-    </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L332" s="3">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="M332" s="3">
+        <f t="shared" si="51"/>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A333" s="3">
         <v>327</v>
       </c>
@@ -8770,8 +11366,16 @@
       <c r="J333" s="3">
         <v>120</v>
       </c>
-    </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L333" s="3">
+        <f t="shared" si="50"/>
+        <v>824</v>
+      </c>
+      <c r="M333" s="3">
+        <f t="shared" si="51"/>
+        <v>960</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A334" s="3">
         <v>328</v>
       </c>
@@ -8790,8 +11394,16 @@
       <c r="J334" s="3">
         <v>317</v>
       </c>
-    </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L334" s="3">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="M334" s="3">
+        <f t="shared" si="51"/>
+        <v>951</v>
+      </c>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A335" s="3">
         <v>329</v>
       </c>
@@ -8810,8 +11422,16 @@
       <c r="J335" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L335" s="3">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="M335" s="3">
+        <f t="shared" si="51"/>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A336" s="3">
         <v>330</v>
       </c>
@@ -8830,8 +11450,16 @@
       <c r="J336" s="3">
         <v>150</v>
       </c>
-    </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L336" s="3">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="M336" s="3">
+        <f t="shared" si="51"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A337" s="3">
         <v>331</v>
       </c>
@@ -8850,8 +11478,16 @@
       <c r="J337" s="3">
         <v>168</v>
       </c>
-    </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L337" s="3">
+        <f t="shared" ref="L337" si="52">E337*I337</f>
+        <v>0</v>
+      </c>
+      <c r="M337" s="3">
+        <f t="shared" ref="M337" si="53">E337*J337</f>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A338" s="3">
         <v>332</v>
       </c>
@@ -8872,8 +11508,16 @@
       <c r="J338" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L338" s="3">
+        <f t="shared" ref="L338:L345" si="54">E338*I338</f>
+        <v>198</v>
+      </c>
+      <c r="M338" s="3">
+        <f t="shared" ref="M338:M345" si="55">E338*J338</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A339" s="3">
         <v>333</v>
       </c>
@@ -8894,8 +11538,16 @@
       <c r="J339" s="3">
         <v>170</v>
       </c>
-    </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L339" s="3">
+        <f t="shared" si="54"/>
+        <v>560</v>
+      </c>
+      <c r="M339" s="3">
+        <f t="shared" si="55"/>
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A340" s="3">
         <v>334</v>
       </c>
@@ -8916,8 +11568,16 @@
       <c r="J340" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L340" s="3">
+        <f t="shared" si="54"/>
+        <v>517.29999999999995</v>
+      </c>
+      <c r="M340" s="3">
+        <f t="shared" si="55"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A341" s="3">
         <v>335</v>
       </c>
@@ -8936,8 +11596,16 @@
       <c r="J341" s="3">
         <v>70</v>
       </c>
-    </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L341" s="3">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="M341" s="3">
+        <f t="shared" si="55"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A342" s="3">
         <v>336</v>
       </c>
@@ -8956,8 +11624,16 @@
       <c r="J342" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L342" s="3">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="M342" s="3">
+        <f t="shared" si="55"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A343" s="4">
         <v>337</v>
       </c>
@@ -8978,8 +11654,16 @@
       <c r="J343" s="3">
         <v>123</v>
       </c>
-    </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L343" s="3">
+        <f t="shared" si="54"/>
+        <v>1440</v>
+      </c>
+      <c r="M343" s="3">
+        <f t="shared" si="55"/>
+        <v>984</v>
+      </c>
+    </row>
+    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A344" s="3">
         <v>338</v>
       </c>
@@ -8999,8 +11683,16 @@
       <c r="J344" s="3">
         <v>125</v>
       </c>
-    </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L344" s="3">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="M344" s="3">
+        <f t="shared" si="55"/>
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A345" s="3">
         <v>339</v>
       </c>
@@ -9019,8 +11711,16 @@
       <c r="J345" s="3">
         <v>150</v>
       </c>
-    </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L345" s="3">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="M345" s="3">
+        <f t="shared" si="55"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A346" s="3">
         <v>340</v>
       </c>
@@ -9041,8 +11741,16 @@
       <c r="J346" s="3">
         <v>250</v>
       </c>
-    </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L346" s="3">
+        <f>C346*I346</f>
+        <v>945</v>
+      </c>
+      <c r="M346" s="3">
+        <f>C346*J346</f>
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A347" s="3">
         <v>341</v>
       </c>
@@ -9063,8 +11771,16 @@
       <c r="J347" s="3">
         <v>250</v>
       </c>
-    </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L347" s="3">
+        <f>C347*I347</f>
+        <v>135</v>
+      </c>
+      <c r="M347" s="3">
+        <f>C347*J347</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A348" s="3">
         <v>342</v>
       </c>
@@ -9085,8 +11801,16 @@
       <c r="J348" s="3">
         <v>70</v>
       </c>
-    </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L348" s="3">
+        <f>E348*I348</f>
+        <v>784</v>
+      </c>
+      <c r="M348" s="3">
+        <f>E348*J348</f>
+        <v>980</v>
+      </c>
+    </row>
+    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A349" s="3">
         <v>343</v>
       </c>
@@ -9107,8 +11831,16 @@
       <c r="J349" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L349" s="3">
+        <f t="shared" ref="L349:L354" si="56">E349*I349</f>
+        <v>945</v>
+      </c>
+      <c r="M349" s="3">
+        <f t="shared" ref="M349:M354" si="57">E349*J349</f>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A350" s="3">
         <v>344</v>
       </c>
@@ -9127,8 +11859,16 @@
       <c r="J350" s="3">
         <v>70</v>
       </c>
-    </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L350" s="3">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="M350" s="3">
+        <f t="shared" si="57"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A351" s="3">
         <v>345</v>
       </c>
@@ -9149,8 +11889,16 @@
       <c r="J351" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L351" s="3">
+        <f t="shared" si="56"/>
+        <v>140</v>
+      </c>
+      <c r="M351" s="3">
+        <f t="shared" si="57"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A352" s="3">
         <v>346</v>
       </c>
@@ -9171,8 +11919,16 @@
       <c r="J352" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L352" s="3">
+        <f t="shared" si="56"/>
+        <v>17110</v>
+      </c>
+      <c r="M352" s="3">
+        <f t="shared" si="57"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A353" s="3">
         <v>347</v>
       </c>
@@ -9191,8 +11947,16 @@
       <c r="J353" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L353" s="3">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="M353" s="3">
+        <f t="shared" si="57"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A354" s="3">
         <v>348</v>
       </c>
@@ -9213,8 +11977,16 @@
       <c r="J354" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L354" s="3">
+        <f t="shared" si="56"/>
+        <v>1080</v>
+      </c>
+      <c r="M354" s="3">
+        <f t="shared" si="57"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A355" s="3">
         <v>349</v>
       </c>
@@ -9235,8 +12007,16 @@
       <c r="J355" s="3">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L355" s="3">
+        <f>D355*I355</f>
+        <v>0</v>
+      </c>
+      <c r="M355" s="3">
+        <f>D355*J355</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A356" s="3">
         <v>350</v>
       </c>
@@ -9259,8 +12039,16 @@
       <c r="J356" s="3">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L356" s="3">
+        <f>D356*I356</f>
+        <v>500</v>
+      </c>
+      <c r="M356" s="3">
+        <f>D356*J356</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A357" s="3">
         <v>351</v>
       </c>
@@ -9281,8 +12069,16 @@
       <c r="J357" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L357" s="3">
+        <f>G357*I357</f>
+        <v>40260</v>
+      </c>
+      <c r="M357" s="3">
+        <f>G357*J357</f>
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A358" s="3">
         <v>352</v>
       </c>
@@ -9302,8 +12098,16 @@
       <c r="J358" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L358" s="3">
+        <f>E358*I358</f>
+        <v>0</v>
+      </c>
+      <c r="M358" s="3">
+        <f>E358*J358</f>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A359" s="3">
         <v>353</v>
       </c>
@@ -9322,8 +12126,16 @@
       <c r="J359" s="3">
         <v>35</v>
       </c>
-    </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L359" s="3">
+        <f t="shared" ref="L359:L372" si="58">E359*I359</f>
+        <v>0</v>
+      </c>
+      <c r="M359" s="3">
+        <f t="shared" ref="M359:M372" si="59">E359*J359</f>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A360" s="3">
         <v>354</v>
       </c>
@@ -9342,8 +12154,16 @@
       <c r="J360" s="3">
         <v>625</v>
       </c>
-    </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L360" s="3">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="M360" s="3">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A361" s="3">
         <v>355</v>
       </c>
@@ -9364,8 +12184,16 @@
       <c r="J361" s="3">
         <v>625</v>
       </c>
-    </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L361" s="3">
+        <f t="shared" si="58"/>
+        <v>1350</v>
+      </c>
+      <c r="M361" s="3">
+        <f t="shared" si="59"/>
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A362" s="3">
         <v>356</v>
       </c>
@@ -9386,8 +12214,16 @@
       <c r="J362" s="3">
         <v>625</v>
       </c>
-    </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L362" s="3">
+        <f t="shared" si="58"/>
+        <v>450</v>
+      </c>
+      <c r="M362" s="3">
+        <f t="shared" si="59"/>
+        <v>625</v>
+      </c>
+    </row>
+    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A363" s="3">
         <v>357</v>
       </c>
@@ -9400,8 +12236,16 @@
       <c r="H363" s="3"/>
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
-    </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L363" s="3">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="M363" s="3">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A364" s="3">
         <v>358</v>
       </c>
@@ -9422,8 +12266,16 @@
       <c r="J364" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L364" s="3">
+        <f t="shared" si="58"/>
+        <v>117</v>
+      </c>
+      <c r="M364" s="3">
+        <f t="shared" si="59"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A365" s="3">
         <v>359</v>
       </c>
@@ -9442,8 +12294,16 @@
       <c r="J365" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L365" s="3">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="M365" s="3">
+        <f t="shared" si="59"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A366" s="3">
         <v>360</v>
       </c>
@@ -9462,8 +12322,16 @@
       <c r="J366" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L366" s="3">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="M366" s="3">
+        <f t="shared" si="59"/>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A367" s="3">
         <v>361</v>
       </c>
@@ -9484,8 +12352,16 @@
       <c r="J367" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L367" s="3">
+        <f t="shared" si="58"/>
+        <v>748</v>
+      </c>
+      <c r="M367" s="3">
+        <f t="shared" si="59"/>
+        <v>825</v>
+      </c>
+    </row>
+    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A368" s="3">
         <v>362</v>
       </c>
@@ -9506,8 +12382,16 @@
       <c r="J368" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L368" s="3">
+        <f t="shared" si="58"/>
+        <v>1729</v>
+      </c>
+      <c r="M368" s="3">
+        <f t="shared" si="59"/>
+        <v>585</v>
+      </c>
+    </row>
+    <row r="369" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A369" s="3">
         <v>363</v>
       </c>
@@ -9528,8 +12412,16 @@
       <c r="J369" s="3">
         <v>85</v>
       </c>
-    </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L369" s="3">
+        <f t="shared" si="58"/>
+        <v>136</v>
+      </c>
+      <c r="M369" s="3">
+        <f t="shared" si="59"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="370" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A370" s="4">
         <v>364</v>
       </c>
@@ -9550,8 +12442,16 @@
       <c r="J370" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L370" s="3">
+        <f t="shared" si="58"/>
+        <v>315</v>
+      </c>
+      <c r="M370" s="3">
+        <f t="shared" si="59"/>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="371" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A371" s="3">
         <v>365</v>
       </c>
@@ -9570,8 +12470,16 @@
       <c r="J371" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L371" s="3">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="M371" s="3">
+        <f t="shared" si="59"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="372" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A372" s="3">
         <v>366</v>
       </c>
@@ -9590,8 +12498,16 @@
       <c r="J372" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L372" s="3">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="M372" s="3">
+        <f t="shared" si="59"/>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="373" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A373" s="3">
         <v>367</v>
       </c>
@@ -9610,8 +12526,16 @@
       <c r="J373" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L373" s="3">
+        <f>F373*I373</f>
+        <v>0</v>
+      </c>
+      <c r="M373" s="3">
+        <f>F373*J373</f>
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A374" s="3">
         <v>368</v>
       </c>
@@ -9631,8 +12555,16 @@
       <c r="J374" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L374" s="3">
+        <f>F374*I374</f>
+        <v>0</v>
+      </c>
+      <c r="M374" s="3">
+        <f>F374*J374</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="375" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A375" s="3">
         <v>369</v>
       </c>
@@ -9654,8 +12586,16 @@
       <c r="J375" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L375" s="3">
+        <f t="shared" ref="L375" si="60">E375*I375</f>
+        <v>390</v>
+      </c>
+      <c r="M375" s="3">
+        <f t="shared" ref="M375" si="61">E375*J375</f>
+        <v>585</v>
+      </c>
+    </row>
+    <row r="376" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A376" s="3">
         <v>370</v>
       </c>
@@ -9674,8 +12614,16 @@
       <c r="J376" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L376" s="3">
+        <f t="shared" ref="L376:L403" si="62">E376*I376</f>
+        <v>0</v>
+      </c>
+      <c r="M376" s="3">
+        <f t="shared" ref="M376:M403" si="63">E376*J376</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="377" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A377" s="3">
         <v>371</v>
       </c>
@@ -9692,8 +12640,16 @@
       <c r="H377" s="3"/>
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
-    </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L377" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M377" s="3">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A378" s="3">
         <v>372</v>
       </c>
@@ -9712,8 +12668,16 @@
       <c r="J378" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L378" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M378" s="3">
+        <f t="shared" si="63"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A379" s="3">
         <v>373</v>
       </c>
@@ -9732,8 +12696,16 @@
       <c r="J379" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L379" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M379" s="3">
+        <f t="shared" si="63"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A380" s="3">
         <v>374</v>
       </c>
@@ -9750,8 +12722,16 @@
       <c r="H380" s="3"/>
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
-    </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L380" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M380" s="3">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A381" s="3">
         <v>375</v>
       </c>
@@ -9770,8 +12750,16 @@
       <c r="J381" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L381" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M381" s="3">
+        <f t="shared" si="63"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A382" s="3">
         <v>376</v>
       </c>
@@ -9790,8 +12778,16 @@
       <c r="J382" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L382" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M382" s="3">
+        <f t="shared" si="63"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A383" s="3">
         <v>377</v>
       </c>
@@ -9810,8 +12806,16 @@
       <c r="J383" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L383" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M383" s="3">
+        <f t="shared" si="63"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A384" s="3">
         <v>378</v>
       </c>
@@ -9828,8 +12832,16 @@
       <c r="H384" s="3"/>
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
-    </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L384" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M384" s="3">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A385" s="3">
         <v>379</v>
       </c>
@@ -9848,8 +12860,16 @@
       <c r="J385" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L385" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M385" s="3">
+        <f t="shared" si="63"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A386" s="3">
         <v>380</v>
       </c>
@@ -9870,8 +12890,16 @@
       <c r="J386" s="3">
         <v>110</v>
       </c>
-    </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L386" s="3">
+        <f t="shared" si="62"/>
+        <v>360</v>
+      </c>
+      <c r="M386" s="3">
+        <f t="shared" si="63"/>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="387" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A387" s="3">
         <v>381</v>
       </c>
@@ -9890,8 +12918,16 @@
       <c r="J387" s="3">
         <v>99</v>
       </c>
-    </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L387" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M387" s="3">
+        <f t="shared" si="63"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="388" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A388" s="3">
         <v>382</v>
       </c>
@@ -9910,8 +12946,16 @@
       <c r="J388" s="3">
         <v>65</v>
       </c>
-    </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L388" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M388" s="3">
+        <f t="shared" si="63"/>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="389" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A389" s="3">
         <v>383</v>
       </c>
@@ -9932,8 +12976,16 @@
       <c r="J389" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L389" s="3">
+        <f t="shared" si="62"/>
+        <v>70</v>
+      </c>
+      <c r="M389" s="3">
+        <f t="shared" si="63"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="390" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A390" s="3">
         <v>384</v>
       </c>
@@ -9954,8 +13006,16 @@
       <c r="J390" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L390" s="3">
+        <f t="shared" si="62"/>
+        <v>57</v>
+      </c>
+      <c r="M390" s="3">
+        <f t="shared" si="63"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="391" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A391" s="3">
         <v>385</v>
       </c>
@@ -9976,8 +13036,16 @@
       <c r="J391" s="3">
         <v>110</v>
       </c>
-    </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L391" s="3">
+        <f t="shared" si="62"/>
+        <v>114</v>
+      </c>
+      <c r="M391" s="3">
+        <f t="shared" si="63"/>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A392" s="3">
         <v>386</v>
       </c>
@@ -9998,8 +13066,16 @@
       <c r="J392" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L392" s="3">
+        <f t="shared" si="62"/>
+        <v>684</v>
+      </c>
+      <c r="M392" s="3">
+        <f t="shared" si="63"/>
+        <v>960</v>
+      </c>
+    </row>
+    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A393" s="3">
         <v>387</v>
       </c>
@@ -10020,8 +13096,16 @@
       <c r="J393" s="3">
         <v>135</v>
       </c>
-    </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L393" s="3">
+        <f t="shared" si="62"/>
+        <v>126</v>
+      </c>
+      <c r="M393" s="3">
+        <f t="shared" si="63"/>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A394" s="3">
         <v>388</v>
       </c>
@@ -10040,8 +13124,16 @@
       <c r="J394" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L394" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M394" s="3">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A395" s="3">
         <v>389</v>
       </c>
@@ -10062,8 +13154,16 @@
       <c r="J395" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L395" s="3">
+        <f t="shared" si="62"/>
+        <v>1566</v>
+      </c>
+      <c r="M395" s="3">
+        <f t="shared" si="63"/>
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A396" s="3">
         <v>390</v>
       </c>
@@ -10084,8 +13184,16 @@
       <c r="J396" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L396" s="3">
+        <f t="shared" si="62"/>
+        <v>783</v>
+      </c>
+      <c r="M396" s="3">
+        <f t="shared" si="63"/>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A397" s="3"/>
       <c r="B397" s="3" t="s">
         <v>382</v>
@@ -10104,8 +13212,16 @@
       <c r="J397" s="3">
         <v>1050</v>
       </c>
-    </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L397" s="3">
+        <f t="shared" si="62"/>
+        <v>747</v>
+      </c>
+      <c r="M397" s="3">
+        <f t="shared" si="63"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="398" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A398" s="3">
         <v>391</v>
       </c>
@@ -10124,8 +13240,16 @@
       <c r="J398" s="3">
         <v>99</v>
       </c>
-    </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L398" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M398" s="3">
+        <f t="shared" si="63"/>
+        <v>495</v>
+      </c>
+    </row>
+    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A399" s="3">
         <v>392</v>
       </c>
@@ -10146,8 +13270,16 @@
       <c r="J399" s="3">
         <v>625</v>
       </c>
-    </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L399" s="3">
+        <f t="shared" si="62"/>
+        <v>1086</v>
+      </c>
+      <c r="M399" s="3">
+        <f t="shared" si="63"/>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A400" s="3">
         <v>393</v>
       </c>
@@ -10166,8 +13298,16 @@
       <c r="J400" s="3">
         <v>342</v>
       </c>
-    </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L400" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M400" s="3">
+        <f t="shared" si="63"/>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A401" s="3">
         <v>394</v>
       </c>
@@ -10186,8 +13326,16 @@
       <c r="J401" s="3">
         <v>349</v>
       </c>
-    </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L401" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="M401" s="3">
+        <f t="shared" si="63"/>
+        <v>349</v>
+      </c>
+    </row>
+    <row r="402" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A402" s="3">
         <v>396</v>
       </c>
@@ -10208,8 +13356,16 @@
       <c r="J402" s="3">
         <v>1500</v>
       </c>
-    </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L402" s="3">
+        <f t="shared" si="62"/>
+        <v>900</v>
+      </c>
+      <c r="M402" s="3">
+        <f t="shared" si="63"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="403" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A403" s="3">
         <v>397</v>
       </c>
@@ -10229,6 +13385,31 @@
       </c>
       <c r="J403" s="3">
         <v>79</v>
+      </c>
+      <c r="L403" s="3">
+        <f t="shared" si="62"/>
+        <v>109</v>
+      </c>
+      <c r="M403" s="3">
+        <f t="shared" si="63"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="404" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L404" s="3"/>
+      <c r="M404" s="3"/>
+    </row>
+    <row r="405" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B405" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="L405" s="10">
+        <f>SUM(L3:L403)</f>
+        <v>303697.05999999988</v>
+      </c>
+      <c r="M405" s="10">
+        <f>SUM(M3:M403)</f>
+        <v>357269.49000000005</v>
       </c>
     </row>
   </sheetData>

--- a/meds/list.xlsx
+++ b/meds/list.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56720AE0-55AE-4751-A825-9B38A563E2E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,12 +30,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="J372" authorId="0" shapeId="0" xr:uid="{C822A8C3-D51B-41F2-A5B7-544A77A781D3}">
+    <comment ref="J372" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -508,9 +507,6 @@
     <t>Moist Max</t>
   </si>
   <si>
-    <t>Befnor</t>
-  </si>
-  <si>
     <t>Icipro</t>
   </si>
   <si>
@@ -529,9 +525,6 @@
     <t>Moist</t>
   </si>
   <si>
-    <t>Sucraf ill</t>
-  </si>
-  <si>
     <t>Evalax</t>
   </si>
   <si>
@@ -1253,12 +1246,18 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Betnor</t>
+  </si>
+  <si>
+    <t>Sucrafil</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1373,17 +1372,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1663,62 +1662,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M405"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7" t="s">
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="10" t="s">
         <v>4</v>
       </c>
       <c r="K1" s="9"/>
-      <c r="L1" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
+      <c r="L1" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
       <c r="C2" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -1726,13 +1725,13 @@
       <c r="H2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
       <c r="K2" s="9"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1764,7 +1763,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1794,7 +1793,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1826,7 +1825,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1856,7 +1855,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1884,7 +1883,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1916,7 +1915,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1946,7 +1945,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1978,7 +1977,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -2008,7 +2007,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -2040,7 +2039,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -2070,7 +2069,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -2100,7 +2099,7 @@
         <v>33.839999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -2132,7 +2131,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -2162,7 +2161,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -2190,7 +2189,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -2222,7 +2221,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -2254,7 +2253,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -2286,7 +2285,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -2316,7 +2315,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -2346,7 +2345,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -2376,7 +2375,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -2404,7 +2403,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -2434,7 +2433,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -2464,7 +2463,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -2495,7 +2494,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -2525,7 +2524,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -2555,7 +2554,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -2585,7 +2584,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -2617,7 +2616,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -2649,7 +2648,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -2679,7 +2678,7 @@
         <v>3360</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -2711,7 +2710,7 @@
         <v>8960</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -2741,7 +2740,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>34</v>
       </c>
@@ -2767,7 +2766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -2799,7 +2798,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>36</v>
       </c>
@@ -2827,7 +2826,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -2853,7 +2852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -2881,7 +2880,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -2913,7 +2912,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -2943,7 +2942,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -2975,7 +2974,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>42</v>
       </c>
@@ -3007,7 +3006,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>43</v>
       </c>
@@ -3039,7 +3038,7 @@
         <v>2880</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>44</v>
       </c>
@@ -3071,7 +3070,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>45</v>
       </c>
@@ -3101,7 +3100,7 @@
         <v>2280</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>46</v>
       </c>
@@ -3131,7 +3130,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>47</v>
       </c>
@@ -3163,7 +3162,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>48</v>
       </c>
@@ -3193,7 +3192,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>49</v>
       </c>
@@ -3225,7 +3224,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>50</v>
       </c>
@@ -3255,7 +3254,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>51</v>
       </c>
@@ -3287,7 +3286,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>52</v>
       </c>
@@ -3315,7 +3314,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>53</v>
       </c>
@@ -3341,7 +3340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>54</v>
       </c>
@@ -3373,7 +3372,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>55</v>
       </c>
@@ -3403,7 +3402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>56</v>
       </c>
@@ -3433,7 +3432,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>57</v>
       </c>
@@ -3465,7 +3464,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>58</v>
       </c>
@@ -3495,7 +3494,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>59</v>
       </c>
@@ -3525,7 +3524,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>60</v>
       </c>
@@ -3557,7 +3556,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>61</v>
       </c>
@@ -3587,7 +3586,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>62</v>
       </c>
@@ -3617,7 +3616,7 @@
         <v>1187.5</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>63</v>
       </c>
@@ -3645,7 +3644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>64</v>
       </c>
@@ -3675,7 +3674,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>65</v>
       </c>
@@ -3705,7 +3704,7 @@
         <v>875.04</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>66</v>
       </c>
@@ -3735,7 +3734,7 @@
         <v>176.98</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>67</v>
       </c>
@@ -3765,7 +3764,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>68</v>
       </c>
@@ -3793,7 +3792,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>69</v>
       </c>
@@ -3823,7 +3822,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>70</v>
       </c>
@@ -3853,7 +3852,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>71</v>
       </c>
@@ -3885,7 +3884,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>72</v>
       </c>
@@ -3915,7 +3914,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>73</v>
       </c>
@@ -3946,7 +3945,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>74</v>
       </c>
@@ -3976,7 +3975,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>75</v>
       </c>
@@ -4006,7 +4005,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>76</v>
       </c>
@@ -4036,7 +4035,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>77</v>
       </c>
@@ -4064,7 +4063,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>78</v>
       </c>
@@ -4092,7 +4091,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>79</v>
       </c>
@@ -4120,7 +4119,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>80</v>
       </c>
@@ -4148,7 +4147,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>81</v>
       </c>
@@ -4176,7 +4175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>82</v>
       </c>
@@ -4206,7 +4205,7 @@
         <v>6400</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>83</v>
       </c>
@@ -4236,7 +4235,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>84</v>
       </c>
@@ -4266,7 +4265,7 @@
         <v>241.5</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>85</v>
       </c>
@@ -4296,7 +4295,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>86</v>
       </c>
@@ -4324,7 +4323,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>87</v>
       </c>
@@ -4354,7 +4353,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>88</v>
       </c>
@@ -4384,7 +4383,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>89</v>
       </c>
@@ -4414,7 +4413,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>90</v>
       </c>
@@ -4446,7 +4445,7 @@
         <v>3740</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>91</v>
       </c>
@@ -4476,7 +4475,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>92</v>
       </c>
@@ -4506,7 +4505,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>93</v>
       </c>
@@ -4536,7 +4535,7 @@
         <v>4875</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>94</v>
       </c>
@@ -4566,7 +4565,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>95</v>
       </c>
@@ -4596,7 +4595,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>96</v>
       </c>
@@ -4626,7 +4625,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>97</v>
       </c>
@@ -4656,7 +4655,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>98</v>
       </c>
@@ -4686,7 +4685,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>99</v>
       </c>
@@ -4716,7 +4715,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>100</v>
       </c>
@@ -4746,7 +4745,7 @@
         <v>165.35999999999999</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>101</v>
       </c>
@@ -4776,7 +4775,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>102</v>
       </c>
@@ -4806,7 +4805,7 @@
         <v>902.5</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>103</v>
       </c>
@@ -4834,7 +4833,7 @@
         <v>318.56</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>104</v>
       </c>
@@ -4864,7 +4863,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>105</v>
       </c>
@@ -4894,7 +4893,7 @@
         <v>1192.5</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>106</v>
       </c>
@@ -4924,7 +4923,7 @@
         <v>414.95</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>107</v>
       </c>
@@ -4952,7 +4951,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>108</v>
       </c>
@@ -4982,7 +4981,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -5002,7 +5001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>109</v>
       </c>
@@ -5030,7 +5029,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>110</v>
       </c>
@@ -5060,7 +5059,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>111</v>
       </c>
@@ -5092,7 +5091,7 @@
         <v>990.01</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>112</v>
       </c>
@@ -5122,7 +5121,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>113</v>
       </c>
@@ -5152,7 +5151,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>114</v>
       </c>
@@ -5184,7 +5183,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>115</v>
       </c>
@@ -5216,7 +5215,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>116</v>
       </c>
@@ -5246,7 +5245,7 @@
         <v>5250</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>117</v>
       </c>
@@ -5276,7 +5275,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>118</v>
       </c>
@@ -5304,7 +5303,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>119</v>
       </c>
@@ -5336,7 +5335,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>120</v>
       </c>
@@ -5366,7 +5365,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>121</v>
       </c>
@@ -5396,7 +5395,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>122</v>
       </c>
@@ -5426,7 +5425,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>123</v>
       </c>
@@ -5454,7 +5453,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>124</v>
       </c>
@@ -5484,7 +5483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>125</v>
       </c>
@@ -5514,7 +5513,7 @@
         <v>262.5</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>126</v>
       </c>
@@ -5544,7 +5543,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>127</v>
       </c>
@@ -5574,7 +5573,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>128</v>
       </c>
@@ -5604,7 +5603,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>129</v>
       </c>
@@ -5632,7 +5631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>130</v>
       </c>
@@ -5658,7 +5657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>131</v>
       </c>
@@ -5688,7 +5687,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>132</v>
       </c>
@@ -5716,7 +5715,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>133</v>
       </c>
@@ -5746,7 +5745,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>134</v>
       </c>
@@ -5776,7 +5775,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>135</v>
       </c>
@@ -5806,7 +5805,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -5820,7 +5819,7 @@
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>136</v>
       </c>
@@ -5850,7 +5849,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>137</v>
       </c>
@@ -5880,7 +5879,7 @@
         <v>317.70000000000005</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>138</v>
       </c>
@@ -5910,7 +5909,7 @@
         <v>191.73</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>139</v>
       </c>
@@ -5929,7 +5928,7 @@
         <v>172.59</v>
       </c>
       <c r="J143" s="3">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="L143" s="3">
         <f t="shared" si="18"/>
@@ -5937,10 +5936,10 @@
       </c>
       <c r="M143" s="3">
         <f t="shared" si="19"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>140</v>
       </c>
@@ -5955,20 +5954,22 @@
       <c r="F144" s="3"/>
       <c r="G144" s="3"/>
       <c r="H144" s="3"/>
-      <c r="I144" s="3"/>
+      <c r="I144" s="3">
+        <v>63.2</v>
+      </c>
       <c r="J144" s="3">
-        <v>100</v>
+        <v>46.1</v>
       </c>
       <c r="L144" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>189.60000000000002</v>
       </c>
       <c r="M144" s="3">
         <f t="shared" si="19"/>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+        <v>138.30000000000001</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>141</v>
       </c>
@@ -5998,7 +5999,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>142</v>
       </c>
@@ -6028,12 +6029,12 @@
         <v>1131.44</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>143</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
@@ -6058,7 +6059,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>144</v>
       </c>
@@ -6088,12 +6089,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>145</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>147</v>
+        <v>394</v>
       </c>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
@@ -6104,26 +6105,26 @@
       <c r="G149" s="3"/>
       <c r="H149" s="3"/>
       <c r="I149" s="3">
-        <v>25.85</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="J149" s="3">
-        <v>30</v>
+        <v>91.97</v>
       </c>
       <c r="L149" s="3">
         <f t="shared" si="18"/>
-        <v>155.10000000000002</v>
+        <v>435.59999999999997</v>
       </c>
       <c r="M149" s="3">
         <f t="shared" si="19"/>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+        <v>551.81999999999994</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>146</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
@@ -6148,12 +6149,12 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>147</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
@@ -6178,12 +6179,12 @@
         <v>412.91999999999996</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>148</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
@@ -6208,12 +6209,12 @@
         <v>360</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>149</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
@@ -6238,12 +6239,12 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>150</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
@@ -6268,12 +6269,12 @@
         <v>400</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>151</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>154</v>
+        <v>395</v>
       </c>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
@@ -6283,25 +6284,27 @@
       <c r="F155" s="3"/>
       <c r="G155" s="3"/>
       <c r="H155" s="3"/>
-      <c r="I155" s="3"/>
+      <c r="I155" s="3">
+        <v>357.75</v>
+      </c>
       <c r="J155" s="3">
-        <v>195</v>
+        <v>472</v>
       </c>
       <c r="L155" s="3">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>715.5</v>
       </c>
       <c r="M155" s="3">
         <f t="shared" si="25"/>
-        <v>390</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>152</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
@@ -6326,12 +6329,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>153</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
@@ -6342,26 +6345,26 @@
       <c r="G157" s="3"/>
       <c r="H157" s="3"/>
       <c r="I157" s="3">
-        <v>387.39</v>
+        <v>291.06</v>
       </c>
       <c r="J157" s="3">
-        <v>280.86</v>
+        <v>337</v>
       </c>
       <c r="L157" s="3">
         <f t="shared" si="24"/>
-        <v>774.78</v>
+        <v>582.12</v>
       </c>
       <c r="M157" s="3">
         <f t="shared" si="25"/>
-        <v>561.72</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>154</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
@@ -6372,26 +6375,26 @@
       <c r="G158" s="3"/>
       <c r="H158" s="3"/>
       <c r="I158" s="3">
-        <v>261.68</v>
+        <v>262.7</v>
       </c>
       <c r="J158" s="3">
-        <v>189.72</v>
+        <v>303.52</v>
       </c>
       <c r="L158" s="3">
         <f t="shared" si="24"/>
-        <v>523.36</v>
+        <v>525.4</v>
       </c>
       <c r="M158" s="3">
         <f t="shared" si="25"/>
-        <v>379.44</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+        <v>607.04</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>155</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
@@ -6402,26 +6405,26 @@
       <c r="G159" s="3"/>
       <c r="H159" s="3"/>
       <c r="I159" s="3">
-        <v>255.73</v>
+        <v>256.72000000000003</v>
       </c>
       <c r="J159" s="3">
-        <v>185.4</v>
+        <v>296.64</v>
       </c>
       <c r="L159" s="3">
         <f t="shared" si="24"/>
-        <v>767.18999999999994</v>
+        <v>770.16000000000008</v>
       </c>
       <c r="M159" s="3">
         <f t="shared" si="25"/>
-        <v>556.20000000000005</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+        <v>889.92</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>156</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
@@ -6432,26 +6435,26 @@
       <c r="G160" s="3"/>
       <c r="H160" s="3"/>
       <c r="I160" s="3">
-        <v>194.25</v>
+        <v>193.1</v>
       </c>
       <c r="J160" s="3">
-        <v>140.83000000000001</v>
+        <v>225.33</v>
       </c>
       <c r="L160" s="3">
         <f t="shared" si="24"/>
-        <v>582.75</v>
+        <v>579.29999999999995</v>
       </c>
       <c r="M160" s="3">
         <f t="shared" si="25"/>
-        <v>422.49</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+        <v>675.99</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>157</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
@@ -6462,26 +6465,26 @@
       <c r="G161" s="3"/>
       <c r="H161" s="3"/>
       <c r="I161" s="3">
-        <v>255.75</v>
+        <v>254.75</v>
       </c>
       <c r="J161" s="3">
-        <v>183.97</v>
+        <v>294.35000000000002</v>
       </c>
       <c r="L161" s="3">
         <f t="shared" si="24"/>
-        <v>511.5</v>
+        <v>509.5</v>
       </c>
       <c r="M161" s="3">
         <f t="shared" si="25"/>
-        <v>367.94</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+        <v>588.70000000000005</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>158</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
@@ -6492,26 +6495,26 @@
       <c r="G162" s="3"/>
       <c r="H162" s="3"/>
       <c r="I162" s="3">
-        <v>232.86</v>
+        <v>163.72999999999999</v>
       </c>
       <c r="J162" s="3">
-        <v>168.83</v>
+        <v>189.93</v>
       </c>
       <c r="L162" s="3">
         <f t="shared" si="24"/>
-        <v>465.72</v>
+        <v>327.45999999999998</v>
       </c>
       <c r="M162" s="3">
         <f t="shared" si="25"/>
-        <v>337.66</v>
-      </c>
-    </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+        <v>379.86</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>159</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
@@ -6536,12 +6539,12 @@
         <v>150</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>160</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
@@ -6551,25 +6554,27 @@
       <c r="F164" s="3"/>
       <c r="G164" s="3"/>
       <c r="H164" s="3"/>
-      <c r="I164" s="3"/>
+      <c r="I164" s="3">
+        <v>88.33</v>
+      </c>
       <c r="J164" s="3">
-        <v>71.5</v>
+        <v>148</v>
       </c>
       <c r="L164" s="3">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>264.99</v>
       </c>
       <c r="M164" s="3">
         <f t="shared" si="25"/>
-        <v>214.5</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>161</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
@@ -6579,25 +6584,27 @@
       <c r="F165" s="3"/>
       <c r="G165" s="3"/>
       <c r="H165" s="3"/>
-      <c r="I165" s="3"/>
+      <c r="I165" s="3">
+        <v>84.97</v>
+      </c>
       <c r="J165" s="3">
         <v>148</v>
       </c>
       <c r="L165" s="3">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>339.88</v>
       </c>
       <c r="M165" s="3">
         <f t="shared" si="25"/>
         <v>592</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>162</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
@@ -6607,20 +6614,22 @@
       <c r="F166" s="3"/>
       <c r="G166" s="3"/>
       <c r="H166" s="3"/>
-      <c r="I166" s="3"/>
+      <c r="I166" s="3">
+        <v>186.9</v>
+      </c>
       <c r="J166" s="3">
-        <v>130.69999999999999</v>
+        <v>220</v>
       </c>
       <c r="L166" s="3">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>560.70000000000005</v>
       </c>
       <c r="M166" s="3">
         <f t="shared" si="25"/>
-        <v>392.09999999999997</v>
-      </c>
-    </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -6634,12 +6643,12 @@
       <c r="L167" s="3"/>
       <c r="M167" s="3"/>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>163</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
@@ -6664,12 +6673,12 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>164</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
@@ -6694,12 +6703,12 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>165</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
@@ -6722,12 +6731,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>166</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
@@ -6752,12 +6761,12 @@
         <v>925</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>167</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
@@ -6782,12 +6791,12 @@
         <v>910</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>168</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
@@ -6812,12 +6821,12 @@
         <v>260</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>169</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
@@ -6842,12 +6851,12 @@
         <v>660</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>170</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
@@ -6872,12 +6881,12 @@
         <v>640</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>171</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
@@ -6902,12 +6911,12 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>172</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
@@ -6932,12 +6941,12 @@
         <v>550</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>173</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
@@ -6962,12 +6971,12 @@
         <v>4940</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>174</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
@@ -6992,12 +7001,12 @@
         <v>288</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>175</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
@@ -7022,12 +7031,12 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>176</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
@@ -7050,12 +7059,12 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>177</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
@@ -7078,12 +7087,12 @@
         <v>234</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>178</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
@@ -7108,12 +7117,12 @@
         <v>800</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>179</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
@@ -7138,12 +7147,12 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>180</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
@@ -7168,12 +7177,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>181</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
@@ -7198,12 +7207,12 @@
         <v>900</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>182</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
@@ -7226,12 +7235,12 @@
         <v>810</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>183</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
@@ -7254,12 +7263,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>184</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
@@ -7284,12 +7293,12 @@
         <v>308</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>185</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
@@ -7314,12 +7323,12 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>186</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
@@ -7342,12 +7351,12 @@
         <v>396</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>187</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
@@ -7372,7 +7381,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>188</v>
       </c>
@@ -7394,12 +7403,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>189</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
@@ -7424,12 +7433,12 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>190</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
@@ -7454,12 +7463,12 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>191</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
@@ -7482,12 +7491,12 @@
         <v>825</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>192</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
@@ -7512,12 +7521,12 @@
         <v>420</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>193</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
@@ -7542,12 +7551,12 @@
         <v>560</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>194</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
@@ -7572,12 +7581,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>195</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
@@ -7602,12 +7611,12 @@
         <v>960</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>196</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
@@ -7632,12 +7641,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>197</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
@@ -7662,12 +7671,12 @@
         <v>166</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>198</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
@@ -7692,12 +7701,12 @@
         <v>440</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>199</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
@@ -7720,12 +7729,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>200</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
@@ -7750,12 +7759,12 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>201</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
@@ -7780,12 +7789,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>202</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
@@ -7810,12 +7819,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>203</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
@@ -7840,12 +7849,12 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>204</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
@@ -7870,12 +7879,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>205</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
@@ -7900,12 +7909,12 @@
         <v>425</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>206</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
@@ -7930,12 +7939,12 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>207</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
@@ -7958,12 +7967,12 @@
         <v>137</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>208</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
@@ -7986,12 +7995,12 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>209</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
@@ -8016,12 +8025,12 @@
         <v>245</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
         <v>210</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
@@ -8046,7 +8055,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>211</v>
       </c>
@@ -8062,7 +8071,7 @@
       <c r="L216" s="3"/>
       <c r="M216" s="3"/>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>212</v>
       </c>
@@ -8078,7 +8087,7 @@
       <c r="L217" s="3"/>
       <c r="M217" s="3"/>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>213</v>
       </c>
@@ -8094,7 +8103,7 @@
       <c r="L218" s="3"/>
       <c r="M218" s="3"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
         <v>214</v>
       </c>
@@ -8110,7 +8119,7 @@
       <c r="L219" s="3"/>
       <c r="M219" s="3"/>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>215</v>
       </c>
@@ -8126,7 +8135,7 @@
       <c r="L220" s="3"/>
       <c r="M220" s="3"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
         <v>216</v>
       </c>
@@ -8142,7 +8151,7 @@
       <c r="L221" s="3"/>
       <c r="M221" s="3"/>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>217</v>
       </c>
@@ -8158,7 +8167,7 @@
       <c r="L222" s="3"/>
       <c r="M222" s="3"/>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>218</v>
       </c>
@@ -8174,7 +8183,7 @@
       <c r="L223" s="3"/>
       <c r="M223" s="3"/>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>219</v>
       </c>
@@ -8190,7 +8199,7 @@
       <c r="L224" s="3"/>
       <c r="M224" s="3"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>220</v>
       </c>
@@ -8206,12 +8215,12 @@
       <c r="L225" s="3"/>
       <c r="M225" s="3"/>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>221</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
@@ -8236,12 +8245,12 @@
         <v>170</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>222</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
@@ -8264,12 +8273,12 @@
         <v>633.6</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>223</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
@@ -8292,12 +8301,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>224</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
@@ -8322,12 +8331,12 @@
         <v>300</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>225</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
@@ -8350,12 +8359,12 @@
         <v>525</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>226</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
@@ -8380,12 +8389,12 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>227</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
@@ -8410,12 +8419,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>228</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
@@ -8440,12 +8449,12 @@
         <v>429</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>229</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
@@ -8470,12 +8479,12 @@
         <v>540</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>230</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
@@ -8500,12 +8509,12 @@
         <v>475</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>231</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
@@ -8530,12 +8539,12 @@
         <v>204</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>232</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
@@ -8560,12 +8569,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>233</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
@@ -8590,12 +8599,12 @@
         <v>330</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>234</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
@@ -8620,12 +8629,12 @@
         <v>725</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>235</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
@@ -8650,12 +8659,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>236</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
@@ -8680,12 +8689,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>237</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
@@ -8710,12 +8719,12 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>238</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
@@ -8740,12 +8749,12 @@
         <v>520</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>239</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
@@ -8770,12 +8779,12 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>240</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
@@ -8798,12 +8807,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>241</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
@@ -8828,12 +8837,12 @@
         <v>260</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>242</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
@@ -8856,12 +8865,12 @@
         <v>660</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>243</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
@@ -8884,12 +8893,12 @@
         <v>960</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
         <v>244</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
@@ -8914,12 +8923,12 @@
         <v>144</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>245</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
@@ -8944,12 +8953,12 @@
         <v>360</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
         <v>246</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
@@ -8974,12 +8983,12 @@
         <v>400</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>247</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
@@ -9004,12 +9013,12 @@
         <v>350</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>248</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
@@ -9034,12 +9043,12 @@
         <v>935</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>249</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
@@ -9064,12 +9073,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
         <v>250</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
@@ -9094,12 +9103,12 @@
         <v>640</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>251</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
@@ -9110,26 +9119,26 @@
       <c r="G256" s="3"/>
       <c r="H256" s="3"/>
       <c r="I256" s="3">
-        <v>239.52</v>
+        <v>240.31</v>
       </c>
       <c r="J256" s="3">
-        <v>173.5</v>
+        <v>277.60000000000002</v>
       </c>
       <c r="L256" s="3">
         <f t="shared" si="32"/>
-        <v>1437.1200000000001</v>
+        <v>1441.8600000000001</v>
       </c>
       <c r="M256" s="3">
         <f t="shared" si="33"/>
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1665.6000000000001</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>252</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
@@ -9154,12 +9163,12 @@
         <v>720</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>253</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
@@ -9184,12 +9193,12 @@
         <v>6360</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>254</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
@@ -9214,12 +9223,12 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>255</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
@@ -9244,12 +9253,12 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
         <v>256</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
@@ -9274,12 +9283,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>257</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
@@ -9304,12 +9313,12 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A263" s="3">
         <v>258</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
@@ -9334,12 +9343,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A264" s="3">
         <v>259</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
@@ -9364,12 +9373,12 @@
         <v>550</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
         <v>260</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
@@ -9388,12 +9397,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A266" s="3">
         <v>261</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
@@ -9418,12 +9427,12 @@
         <v>870</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A267" s="3">
         <v>262</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
@@ -9448,12 +9457,12 @@
         <v>665</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A268" s="3">
         <v>263</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
@@ -9476,12 +9485,12 @@
         <v>143</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A269" s="3">
         <v>264</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
@@ -9504,12 +9513,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
         <v>265</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
@@ -9534,12 +9543,12 @@
         <v>604</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A271" s="3">
         <v>266</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
@@ -9564,12 +9573,12 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A272" s="3">
         <v>267</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
@@ -9594,12 +9603,12 @@
         <v>580</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A273" s="3">
         <v>268</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
@@ -9624,12 +9633,12 @@
         <v>525</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A274" s="3">
         <v>269</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
@@ -9654,12 +9663,12 @@
         <v>540</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A275" s="3">
         <v>270</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
@@ -9684,12 +9693,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A276" s="3">
         <v>271</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
@@ -9712,12 +9721,12 @@
         <v>525</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A277" s="3">
         <v>272</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
@@ -9740,12 +9749,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A278" s="3">
         <v>273</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
@@ -9770,12 +9779,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
         <v>274</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
@@ -9800,12 +9809,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
         <v>275</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
@@ -9830,12 +9839,12 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
         <v>276</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
@@ -9860,12 +9869,12 @@
         <v>4650</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
         <v>277</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
@@ -9890,12 +9899,12 @@
         <v>3510</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A283" s="3">
         <v>278</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
@@ -9920,12 +9929,12 @@
         <v>490</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
         <v>279</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
@@ -9948,12 +9957,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A285" s="3">
         <v>280</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
@@ -9978,12 +9987,12 @@
         <v>400</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
         <v>281</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
@@ -10006,12 +10015,12 @@
         <v>300</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A287" s="4">
         <v>282</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
@@ -10036,12 +10045,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
         <v>283</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
@@ -10066,12 +10075,12 @@
         <v>750</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A289" s="3">
         <v>284</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
@@ -10094,12 +10103,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A290" s="3">
         <v>285</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
@@ -10122,12 +10131,12 @@
         <v>700</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A291" s="3">
         <v>286</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
@@ -10152,12 +10161,12 @@
         <v>530</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A292" s="3">
         <v>287</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
@@ -10182,12 +10191,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A293" s="3">
         <v>288</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
@@ -10210,12 +10219,12 @@
         <v>260</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A294" s="3">
         <v>289</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
@@ -10238,12 +10247,12 @@
         <v>400</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A295" s="3">
         <v>290</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
@@ -10266,12 +10275,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A296" s="3">
         <v>291</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
@@ -10294,12 +10303,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A297" s="3">
         <v>292</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
@@ -10322,12 +10331,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A298" s="3">
         <v>293</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
@@ -10352,12 +10361,12 @@
         <v>890</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A299" s="3">
         <v>294</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
@@ -10382,12 +10391,12 @@
         <v>890</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A300" s="3">
         <v>295</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
@@ -10412,12 +10421,12 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A301" s="3">
         <v>296</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
@@ -10442,12 +10451,12 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A302" s="3">
         <v>297</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
@@ -10472,12 +10481,12 @@
         <v>526</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A303" s="3">
         <v>298</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
@@ -10502,12 +10511,12 @@
         <v>552</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A304" s="3">
         <v>299</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
@@ -10532,12 +10541,12 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A305" s="3">
         <v>300</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
@@ -10562,12 +10571,12 @@
         <v>571</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A306" s="3">
         <v>301</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
@@ -10592,12 +10601,12 @@
         <v>580</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A307" s="3">
         <v>302</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
@@ -10620,10 +10629,10 @@
         <v>118</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A308" s="3"/>
       <c r="B308" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
@@ -10646,12 +10655,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A309" s="3">
         <v>303</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
@@ -10674,12 +10683,12 @@
         <v>297</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
         <v>304</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
@@ -10704,12 +10713,12 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A311" s="3">
         <v>305</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
@@ -10734,12 +10743,12 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A312" s="3">
         <v>306</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
@@ -10764,12 +10773,12 @@
         <v>420</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A313" s="3">
         <v>307</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
@@ -10794,12 +10803,12 @@
         <v>195</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A314" s="3">
         <v>308</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
@@ -10824,12 +10833,12 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
         <v>309</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
@@ -10852,12 +10861,12 @@
         <v>550</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A316" s="3">
         <v>310</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
@@ -10879,12 +10888,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A317" s="3">
         <v>311</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
@@ -10909,12 +10918,12 @@
         <v>4720</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A318" s="3">
         <v>312</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
@@ -10939,12 +10948,12 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A319" s="3">
         <v>313</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
@@ -10969,12 +10978,12 @@
         <v>765</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A320" s="3">
         <v>314</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
@@ -11001,12 +11010,12 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A321" s="3">
         <v>315</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
@@ -11029,12 +11038,12 @@
         <v>560</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
         <v>316</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
@@ -11059,12 +11068,12 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A323" s="3">
         <v>317</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
@@ -11091,12 +11100,12 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A324" s="3">
         <v>318</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
@@ -11119,12 +11128,12 @@
         <v>800</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A325" s="3">
         <v>319</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
@@ -11147,12 +11156,12 @@
         <v>285</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A326" s="3">
         <v>320</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C326" s="3"/>
       <c r="D326" s="3"/>
@@ -11177,12 +11186,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A327" s="3">
         <v>321</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
@@ -11205,12 +11214,12 @@
         <v>360</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A328" s="3">
         <v>322</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
@@ -11233,12 +11242,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A329" s="3">
         <v>323</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
@@ -11261,12 +11270,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A330" s="3">
         <v>324</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
@@ -11289,12 +11298,12 @@
         <v>480</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A331" s="3">
         <v>325</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
@@ -11317,12 +11326,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A332" s="3">
         <v>326</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
@@ -11345,12 +11354,12 @@
         <v>314</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A333" s="3">
         <v>327</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
@@ -11375,12 +11384,12 @@
         <v>960</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A334" s="3">
         <v>328</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
@@ -11403,12 +11412,12 @@
         <v>951</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A335" s="3">
         <v>329</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
@@ -11431,12 +11440,12 @@
         <v>145</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A336" s="3">
         <v>330</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
@@ -11459,12 +11468,12 @@
         <v>450</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A337" s="3">
         <v>331</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
@@ -11487,12 +11496,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A338" s="3">
         <v>332</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
@@ -11517,12 +11526,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A339" s="3">
         <v>333</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
@@ -11547,12 +11556,12 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A340" s="3">
         <v>334</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
@@ -11577,12 +11586,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A341" s="3">
         <v>335</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
@@ -11605,12 +11614,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A342" s="3">
         <v>336</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
@@ -11633,12 +11642,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
         <v>337</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
@@ -11663,12 +11672,12 @@
         <v>984</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A344" s="3">
         <v>338</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
@@ -11692,12 +11701,12 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A345" s="3">
         <v>339</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
@@ -11720,12 +11729,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A346" s="3">
         <v>340</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C346" s="3">
         <v>7</v>
@@ -11750,12 +11759,12 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A347" s="3">
         <v>341</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C347" s="3">
         <v>1</v>
@@ -11780,12 +11789,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A348" s="3">
         <v>342</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
@@ -11810,12 +11819,12 @@
         <v>980</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A349" s="3">
         <v>343</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
@@ -11840,12 +11849,12 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A350" s="3">
         <v>344</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C350" s="3"/>
       <c r="D350" s="3"/>
@@ -11868,12 +11877,12 @@
         <v>140</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A351" s="3">
         <v>345</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C351" s="3"/>
       <c r="D351" s="3"/>
@@ -11898,12 +11907,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A352" s="3">
         <v>346</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C352" s="3"/>
       <c r="D352" s="3"/>
@@ -11928,12 +11937,12 @@
         <v>295</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A353" s="3">
         <v>347</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C353" s="3"/>
       <c r="D353" s="3"/>
@@ -11956,12 +11965,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A354" s="3">
         <v>348</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C354" s="3"/>
       <c r="D354" s="3"/>
@@ -11986,12 +11995,12 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A355" s="3">
         <v>349</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C355" s="3"/>
       <c r="D355" s="3">
@@ -12016,12 +12025,12 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A356" s="3">
         <v>350</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C356" s="3"/>
       <c r="D356" s="3">
@@ -12048,12 +12057,12 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A357" s="3">
         <v>351</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C357" s="3"/>
       <c r="D357" s="3"/>
@@ -12078,12 +12087,12 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A358" s="3">
         <v>352</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C358" s="3"/>
       <c r="D358" s="3"/>
@@ -12107,12 +12116,12 @@
         <v>690</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A359" s="3">
         <v>353</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C359" s="3"/>
       <c r="D359" s="3"/>
@@ -12135,12 +12144,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A360" s="3">
         <v>354</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C360" s="3"/>
       <c r="D360" s="3"/>
@@ -12163,12 +12172,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A361" s="3">
         <v>355</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C361" s="3"/>
       <c r="D361" s="3"/>
@@ -12193,12 +12202,12 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A362" s="3">
         <v>356</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C362" s="3"/>
       <c r="D362" s="3"/>
@@ -12223,7 +12232,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A363" s="3">
         <v>357</v>
       </c>
@@ -12245,12 +12254,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A364" s="3">
         <v>358</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C364" s="3"/>
       <c r="D364" s="3"/>
@@ -12275,12 +12284,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A365" s="3">
         <v>359</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C365" s="3"/>
       <c r="D365" s="3"/>
@@ -12303,12 +12312,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A366" s="3">
         <v>360</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C366" s="3"/>
       <c r="D366" s="3"/>
@@ -12331,12 +12340,12 @@
         <v>270</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A367" s="3">
         <v>361</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C367" s="3"/>
       <c r="D367" s="3"/>
@@ -12361,12 +12370,12 @@
         <v>825</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A368" s="3">
         <v>362</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C368" s="3"/>
       <c r="D368" s="3"/>
@@ -12391,12 +12400,12 @@
         <v>585</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A369" s="3">
         <v>363</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C369" s="3"/>
       <c r="D369" s="3"/>
@@ -12421,12 +12430,12 @@
         <v>170</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A370" s="4">
         <v>364</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C370" s="3"/>
       <c r="D370" s="3"/>
@@ -12451,12 +12460,12 @@
         <v>405</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A371" s="3">
         <v>365</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C371" s="3"/>
       <c r="D371" s="3"/>
@@ -12479,12 +12488,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A372" s="3">
         <v>366</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C372" s="3"/>
       <c r="D372" s="3"/>
@@ -12507,12 +12516,12 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A373" s="3">
         <v>367</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C373" s="3"/>
       <c r="D373" s="3"/>
@@ -12535,12 +12544,12 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A374" s="3">
         <v>368</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C374" s="3"/>
       <c r="D374" s="3"/>
@@ -12564,12 +12573,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A375" s="3">
         <v>369</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C375" s="3"/>
       <c r="D375" s="3"/>
@@ -12595,12 +12604,12 @@
         <v>585</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A376" s="3">
         <v>370</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
@@ -12623,12 +12632,12 @@
         <v>800</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A377" s="3">
         <v>371</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C377" s="3"/>
       <c r="D377" s="3"/>
@@ -12649,12 +12658,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A378" s="3">
         <v>372</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C378" s="3"/>
       <c r="D378" s="3"/>
@@ -12677,12 +12686,12 @@
         <v>300</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A379" s="3">
         <v>373</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
@@ -12705,12 +12714,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A380" s="3">
         <v>374</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
@@ -12731,12 +12740,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A381" s="3">
         <v>375</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
@@ -12759,12 +12768,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A382" s="3">
         <v>376</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C382" s="3"/>
       <c r="D382" s="3"/>
@@ -12787,12 +12796,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A383" s="3">
         <v>377</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C383" s="3"/>
       <c r="D383" s="3"/>
@@ -12815,12 +12824,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A384" s="3">
         <v>378</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C384" s="3"/>
       <c r="D384" s="3"/>
@@ -12841,12 +12850,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A385" s="3">
         <v>379</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C385" s="3"/>
       <c r="D385" s="3"/>
@@ -12869,12 +12878,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A386" s="3">
         <v>380</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C386" s="3"/>
       <c r="D386" s="3"/>
@@ -12899,12 +12908,12 @@
         <v>440</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A387" s="3">
         <v>381</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C387" s="3"/>
       <c r="D387" s="3"/>
@@ -12927,12 +12936,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A388" s="3">
         <v>382</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C388" s="3"/>
       <c r="D388" s="3"/>
@@ -12955,12 +12964,12 @@
         <v>260</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A389" s="3">
         <v>383</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C389" s="3"/>
       <c r="D389" s="3"/>
@@ -12985,12 +12994,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A390" s="3">
         <v>384</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C390" s="3"/>
       <c r="D390" s="3"/>
@@ -13015,12 +13024,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A391" s="3">
         <v>385</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C391" s="3"/>
       <c r="D391" s="3"/>
@@ -13045,12 +13054,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A392" s="3">
         <v>386</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C392" s="3"/>
       <c r="D392" s="3"/>
@@ -13075,12 +13084,12 @@
         <v>960</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A393" s="3">
         <v>387</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C393" s="3"/>
       <c r="D393" s="3"/>
@@ -13105,12 +13114,12 @@
         <v>270</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A394" s="3">
         <v>388</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C394" s="3"/>
       <c r="D394" s="3"/>
@@ -13133,12 +13142,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A395" s="3">
         <v>389</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C395" s="3"/>
       <c r="D395" s="3"/>
@@ -13163,12 +13172,12 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A396" s="3">
         <v>390</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C396" s="3"/>
       <c r="D396" s="3"/>
@@ -13193,10 +13202,10 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A397" s="3"/>
       <c r="B397" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C397" s="3"/>
       <c r="D397" s="3"/>
@@ -13221,12 +13230,12 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A398" s="3">
         <v>391</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C398" s="3"/>
       <c r="D398" s="3"/>
@@ -13249,12 +13258,12 @@
         <v>495</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A399" s="3">
         <v>392</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C399" s="3"/>
       <c r="D399" s="3"/>
@@ -13279,12 +13288,12 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A400" s="3">
         <v>393</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C400" s="3"/>
       <c r="D400" s="3"/>
@@ -13307,12 +13316,12 @@
         <v>342</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A401" s="3">
         <v>394</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C401" s="3"/>
       <c r="D401" s="3"/>
@@ -13335,12 +13344,12 @@
         <v>349</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A402" s="3">
         <v>396</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C402" s="3"/>
       <c r="D402" s="3"/>
@@ -13365,12 +13374,12 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A403" s="3">
         <v>397</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C403" s="3"/>
       <c r="D403" s="3"/>
@@ -13395,21 +13404,21 @@
         <v>79</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L404" s="3"/>
       <c r="M404" s="3"/>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B405" s="8" t="s">
-        <v>395</v>
-      </c>
-      <c r="L405" s="10">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B405" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="L405" s="7">
         <f>SUM(L3:L403)</f>
-        <v>303697.05999999988</v>
-      </c>
-      <c r="M405" s="10">
+        <v>305721.60999999987</v>
+      </c>
+      <c r="M405" s="7">
         <f>SUM(M3:M403)</f>
-        <v>357269.49000000005</v>
+        <v>360939.67000000004</v>
       </c>
     </row>
   </sheetData>
